--- a/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
@@ -1300,8 +1300,12 @@
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
-        <v>10</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APPROVED HYDROGEN-STATION ALUMINIUM SUPPLY BOUNDARY, issue70,2026-10-18. Wulf etal2018 DOI10.1016/j.jclepro.2018.07.180,publicsupplement https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx TablesS4,S6:499kgAluminum/station and6kgAluminum per10kgH2storagecapacity. NoAlLi,Li,Ag orZrgrade is specified. Replace the AlLi aerospacealloy proxy only in refuellingstation499kgAluminum input andhighpressuretank0.6kgAluminum perkgH2capacity. Use existing genericwroughtalloy supply as forming-compatibleengineeringreference for unspecifiedrolledAl,not a claim the source identified6061or pureprimaryAl. Preservematerialmass andexistingmetalworking/sheetrolling separately. Do not set allalloyingmetals tozero:theordinarywroughtalloy supplier retainsits ownaveragecomposition/supplymix. SourcegivesnoevidenceforAlLi-specificLi/Ag/Zr additions intheseconsumers. Actualalloygrade,linerstrength,purity,formingyield andtankdesign remainunverified. Tankcapacity-versusdrymass andlifetimes are resolvedinissue71 ratherthan secretlyrenormalizedhere. OthernativeAlLi consumers andtruck/bus/rail referenceinventories unchanged;no globalCF oralloymarketedit. Existinglifecycleandwasteboundaryunchanged:stationhasconcrete treatmentbutnometal-specificEOL,which remainsa coveragegap,no extrarecoverycredit. Applycurrentversionmigrations withsource3.7 identities.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+LCI of basic hydrogen fueling station for 850 kg/d based on (Burkhardt et al., 2016). Utilization factor of 70%, so demand is 595 kg H2/day. Assumed lifetime of 40 years. Two tanks of 125 kg of H2 storage capacity are needed within this lifetime.</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
@@ -1523,8 +1527,10 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>36</v>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
       </c>
       <c r="B20">
         <v>499</v>
@@ -1532,8 +1538,10 @@
       <c r="C20" t="s">
         <v>20</v>
       </c>
-      <c r="D20" t="s">
-        <v>2</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E20" t="s">
         <v>21</v>
@@ -1541,8 +1549,10 @@
       <c r="G20" t="s">
         <v>22</v>
       </c>
-      <c r="I20" t="s">
-        <v>37</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
       </c>
     </row>
     <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.2">
@@ -1737,8 +1747,12 @@
       <c r="A34" t="s">
         <v>9</v>
       </c>
-      <c r="B34" t="s">
-        <v>50</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>APPROVED HYDROGEN-STATION ALUMINIUM SUPPLY BOUNDARY, issue70,2026-10-18. Wulf etal2018 DOI10.1016/j.jclepro.2018.07.180,publicsupplement https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx TablesS4,S6:499kgAluminum/station and6kgAluminum per10kgH2storagecapacity. NoAlLi,Li,Ag orZrgrade is specified. Replace the AlLi aerospacealloy proxy only in refuellingstation499kgAluminum input andhighpressuretank0.6kgAluminum perkgH2capacity. Use existing genericwroughtalloy supply as forming-compatibleengineeringreference for unspecifiedrolledAl,not a claim the source identified6061or pureprimaryAl. Preservematerialmass andexistingmetalworking/sheetrolling separately. Do not set allalloyingmetals tozero:theordinarywroughtalloy supplier retainsits ownaveragecomposition/supplymix. SourcegivesnoevidenceforAlLi-specificLi/Ag/Zr additions intheseconsumers. Actualalloygrade,linerstrength,purity,formingyield andtankdesign remainunverified. Tankcapacity-versusdrymass andlifetimes are resolvedinissue71 ratherthan secretlyrenormalizedhere. OthernativeAlLi consumers andtruck/bus/rail referenceinventories unchanged;no globalCF oralloymarketedit. Existinglifecycleandwasteboundaryunchanged:stationhasconcrete treatmentbutnometal-specificEOL,which remainsa coveragegap,no extrarecoverycredit. Applycurrentversionmigrations withsource3.7 identities.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+LCI for a high pressure storage tank per 1 kg hydrogen (Boureima et al., 2011; Das, 2011). Assumed lifetime of 20 years.</t>
+        </is>
       </c>
     </row>
     <row r="35" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1822,8 +1836,10 @@
       </c>
     </row>
     <row r="39" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>36</v>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
       </c>
       <c r="B39">
         <v>0.6</v>
@@ -1831,8 +1847,10 @@
       <c r="C39" t="s">
         <v>20</v>
       </c>
-      <c r="D39" t="s">
-        <v>2</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E39" t="s">
         <v>21</v>
@@ -1840,8 +1858,10 @@
       <c r="G39" t="s">
         <v>22</v>
       </c>
-      <c r="I39" t="s">
-        <v>37</v>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
       </c>
     </row>
     <row r="40" spans="1:16" ht="16" x14ac:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
@@ -1231,7 +1231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T364"/>
+  <dimension ref="A1:T385"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44.5" customWidth="1"/>
@@ -1302,7 +1302,9 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APPROVED HYDROGEN-STATION ALUMINIUM SUPPLY BOUNDARY, issue70,2026-10-18. Wulf etal2018 DOI10.1016/j.jclepro.2018.07.180,publicsupplement https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx TablesS4,S6:499kgAluminum/station and6kgAluminum per10kgH2storagecapacity. NoAlLi,Li,Ag orZrgrade is specified. Replace the AlLi aerospacealloy proxy only in refuellingstation499kgAluminum input andhighpressuretank0.6kgAluminum perkgH2capacity. Use existing genericwroughtalloy supply as forming-compatibleengineeringreference for unspecifiedrolledAl,not a claim the source identified6061or pureprimaryAl. Preservematerialmass andexistingmetalworking/sheetrolling separately. Do not set allalloyingmetals tozero:theordinarywroughtalloy supplier retainsits ownaveragecomposition/supplymix. SourcegivesnoevidenceforAlLi-specificLi/Ag/Zr additions intheseconsumers. Actualalloygrade,linerstrength,purity,formingyield andtankdesign remainunverified. Tankcapacity-versusdrymass andlifetimes are resolvedinissue71 ratherthan secretlyrenormalizedhere. OthernativeAlLi consumers andtruck/bus/rail referenceinventories unchanged;no globalCF oralloymarketedit. Existinglifecycleandwasteboundaryunchanged:stationhasconcrete treatmentbutnometal-specificEOL,which remainsa coveragegap,no extrarecoverycredit. Applycurrentversionmigrations withsource3.7 identities.
+          <t>APPROVED HYDROGEN-STATION TANK CAPACITY/LIFE UNITS, issue71,2026-10-18. Wulf2018 publicSI DOI10.1016/j.jclepro.2018.07.180 TablesS6(per10kgH2storage) andS8(125kgH2storageforstation),plus workbook40yearstation/20yeartanklife assumptions. TheSI explicitlylists125kg for LOHC,pipelineandhighpressuretruckstation supplypaths. Originaltankkgoutput is kgH2STORAGECAPACITY,notkgdryvessel; sourceS6materials per10kgH2are6Al+9stainless+71.4carbonfiber+30.6epoxy+9lowalloysteel=126kgdry=&gt;12.6kgdry/kgH2capacity. Do not normalize126kgmaterial to10kgdrytank. Stationinstalledcapacity125kgH2 fromS8,20yearvessellife and40yearstationlife implytwo manufacturedsets inone40yearstationinventory,not two125kgvesselsinstalledandthenanotherreplacementfactor. Newunitprovider is one125kgH2capacity installedtankreference containing1575kgdrymaterial,includingits existingtankBoPproportions; sourcepressure,individualcylindercount andcertification unspecified,not labelled700barorbusType4without evidence. Stationbuystwounits total250kgH2capacity manufacture/3150kgdry overlife,exactlypreservingoriginalmaterial,processenergyandformingvectors afterissue70. No hiddennewrecyclingcredit,treatmentorsecondlifetime divisor; originalstationgenericEOLgap remains. Theoriginalkgprovider remainsavailableaslegacycapacityreference withclarifiedcomment,soexternalconsumers donot silently changefunctionalunit. Newexplicitunitprovider is activeforstationonly. Cylinderpressure/reserve/actualhydrogenusablefraction anddemandutilization arestillengineeringgaps. Existing850kg/daynameplate,70%utilization,595kg/dayhydrogen throughput and40yearserviceallocation are unchanged; no operationalcompression/precooling change. Neither3160kgwetmassnorstoredhydrogenfeed ismanufacturedmetal.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED HYDROGEN-STATION ALUMINIUM SUPPLY BOUNDARY, issue70,2026-10-18. Wulf etal2018 DOI10.1016/j.jclepro.2018.07.180,publicsupplement https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx TablesS4,S6:499kgAluminum/station and6kgAluminum per10kgH2storagecapacity. NoAlLi,Li,Ag orZrgrade is specified. Replace the AlLi aerospacealloy proxy only in refuellingstation499kgAluminum input andhighpressuretank0.6kgAluminum perkgH2capacity. Use existing genericwroughtalloy supply as forming-compatibleengineeringreference for unspecifiedrolledAl,not a claim the source identified6061or pureprimaryAl. Preservematerialmass andexistingmetalworking/sheetrolling separately. Do not set allalloyingmetals tozero:theordinarywroughtalloy supplier retainsits ownaveragecomposition/supplymix. SourcegivesnoevidenceforAlLi-specificLi/Ag/Zr additions intheseconsumers. Actualalloygrade,linerstrength,purity,formingyield andtankdesign remainunverified. Tankcapacity-versusdrymass andlifetimes are resolvedinissue71 ratherthan secretlyrenormalizedhere. OthernativeAlLi consumers andtruck/bus/rail referenceinventories unchanged;no globalCF oralloymarketedit. Existinglifecycleandwasteboundaryunchanged:stationhasconcrete treatmentbutnometal-specificEOL,which remainsa coveragegap,no extrarecoverycredit. Applycurrentversionmigrations withsource3.7 identities.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 LCI of basic hydrogen fueling station for 850 kg/d based on (Burkhardt et al., 2016). Utilization factor of 70%, so demand is 595 kg H2/day. Assumed lifetime of 40 years. Two tanks of 125 kg of H2 storage capacity are needed within this lifetime.</t>
         </is>
@@ -1673,26 +1675,34 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>111</v>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>hydrogen storage tank system, station125kg H2 capacity, engineering reference</t>
+        </is>
       </c>
       <c r="B26">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="C26" t="s">
         <v>17</v>
       </c>
-      <c r="D26" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" t="s">
-        <v>21</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
       <c r="G26" t="s">
         <v>22</v>
       </c>
-      <c r="I26" t="s">
-        <v>111</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>hydrogen storage tank system, station125kg H2 capacity, engineering reference</t>
+        </is>
       </c>
     </row>
     <row r="28" spans="1:9" ht="16" x14ac:dyDescent="0.2">
@@ -1749,7 +1759,9 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>APPROVED HYDROGEN-STATION ALUMINIUM SUPPLY BOUNDARY, issue70,2026-10-18. Wulf etal2018 DOI10.1016/j.jclepro.2018.07.180,publicsupplement https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx TablesS4,S6:499kgAluminum/station and6kgAluminum per10kgH2storagecapacity. NoAlLi,Li,Ag orZrgrade is specified. Replace the AlLi aerospacealloy proxy only in refuellingstation499kgAluminum input andhighpressuretank0.6kgAluminum perkgH2capacity. Use existing genericwroughtalloy supply as forming-compatibleengineeringreference for unspecifiedrolledAl,not a claim the source identified6061or pureprimaryAl. Preservematerialmass andexistingmetalworking/sheetrolling separately. Do not set allalloyingmetals tozero:theordinarywroughtalloy supplier retainsits ownaveragecomposition/supplymix. SourcegivesnoevidenceforAlLi-specificLi/Ag/Zr additions intheseconsumers. Actualalloygrade,linerstrength,purity,formingyield andtankdesign remainunverified. Tankcapacity-versusdrymass andlifetimes are resolvedinissue71 ratherthan secretlyrenormalizedhere. OthernativeAlLi consumers andtruck/bus/rail referenceinventories unchanged;no globalCF oralloymarketedit. Existinglifecycleandwasteboundaryunchanged:stationhasconcrete treatmentbutnometal-specificEOL,which remainsa coveragegap,no extrarecoverycredit. Applycurrentversionmigrations withsource3.7 identities.
+          <t>APPROVED HYDROGEN-STATION TANK CAPACITY/LIFE UNITS, issue71,2026-10-18. Wulf2018 publicSI DOI10.1016/j.jclepro.2018.07.180 TablesS6(per10kgH2storage) andS8(125kgH2storageforstation),plus workbook40yearstation/20yeartanklife assumptions. TheSI explicitlylists125kg for LOHC,pipelineandhighpressuretruckstation supplypaths. Originaltankkgoutput is kgH2STORAGECAPACITY,notkgdryvessel; sourceS6materials per10kgH2are6Al+9stainless+71.4carbonfiber+30.6epoxy+9lowalloysteel=126kgdry=&gt;12.6kgdry/kgH2capacity. Do not normalize126kgmaterial to10kgdrytank. Stationinstalledcapacity125kgH2 fromS8,20yearvessellife and40yearstationlife implytwo manufacturedsets inone40yearstationinventory,not two125kgvesselsinstalledandthenanotherreplacementfactor. Newunitprovider is one125kgH2capacity installedtankreference containing1575kgdrymaterial,includingits existingtankBoPproportions; sourcepressure,individualcylindercount andcertification unspecified,not labelled700barorbusType4without evidence. Stationbuystwounits total250kgH2capacity manufacture/3150kgdry overlife,exactlypreservingoriginalmaterial,processenergyandformingvectors afterissue70. No hiddennewrecyclingcredit,treatmentorsecondlifetime divisor; originalstationgenericEOLgap remains. Theoriginalkgprovider remainsavailableaslegacycapacityreference withclarifiedcomment,soexternalconsumers donot silently changefunctionalunit. Newexplicitunitprovider is activeforstationonly. Cylinderpressure/reserve/actualhydrogenusablefraction anddemandutilization arestillengineeringgaps. Existing850kg/daynameplate,70%utilization,595kg/dayhydrogen throughput and40yearserviceallocation are unchanged; no operationalcompression/precooling change. Neither3160kgwetmassnorstoredhydrogenfeed ismanufacturedmetal.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED HYDROGEN-STATION ALUMINIUM SUPPLY BOUNDARY, issue70,2026-10-18. Wulf etal2018 DOI10.1016/j.jclepro.2018.07.180,publicsupplement https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx TablesS4,S6:499kgAluminum/station and6kgAluminum per10kgH2storagecapacity. NoAlLi,Li,Ag orZrgrade is specified. Replace the AlLi aerospacealloy proxy only in refuellingstation499kgAluminum input andhighpressuretank0.6kgAluminum perkgH2capacity. Use existing genericwroughtalloy supply as forming-compatibleengineeringreference for unspecifiedrolledAl,not a claim the source identified6061or pureprimaryAl. Preservematerialmass andexistingmetalworking/sheetrolling separately. Do not set allalloyingmetals tozero:theordinarywroughtalloy supplier retainsits ownaveragecomposition/supplymix. SourcegivesnoevidenceforAlLi-specificLi/Ag/Zr additions intheseconsumers. Actualalloygrade,linerstrength,purity,formingyield andtankdesign remainunverified. Tankcapacity-versusdrymass andlifetimes are resolvedinissue71 ratherthan secretlyrenormalizedhere. OthernativeAlLi consumers andtruck/bus/rail referenceinventories unchanged;no globalCF oralloymarketedit. Existinglifecycleandwasteboundaryunchanged:stationhasconcrete treatmentbutnometal-specificEOL,which remainsa coveragegap,no extrarecoverycredit. Applycurrentversionmigrations withsource3.7 identities.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 LCI for a high pressure storage tank per 1 kg hydrogen (Boureima et al., 2011; Das, 2011). Assumed lifetime of 20 years.</t>
         </is>
@@ -11109,6 +11121,492 @@
         <v>147</v>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>hydrogen storage tank system, station125kg H2 capacity, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>hydrogen storage tank system, station125kg H2 capacity, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Wulf2018 publicSI DOI10.1016/j.jclepro.2018.07.180 TablesS6(per10kgH2storage) andS8(125kgH2storageforstation),plus workbook40yearstation/20yeartanklife assumptions. TheSI explicitlylists125kg for LOHC,pipelineandhighpressuretruckstation supplypaths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>APPROVED HYDROGEN-STATION TANK CAPACITY/LIFE UNITS, issue71,2026-10-18. Wulf2018 publicSI DOI10.1016/j.jclepro.2018.07.180 TablesS6(per10kgH2storage) andS8(125kgH2storageforstation),plus workbook40yearstation/20yeartanklife assumptions. TheSI explicitlylists125kg for LOHC,pipelineandhighpressuretruckstation supplypaths. Originaltankkgoutput is kgH2STORAGECAPACITY,notkgdryvessel; sourceS6materials per10kgH2are6Al+9stainless+71.4carbonfiber+30.6epoxy+9lowalloysteel=126kgdry=&gt;12.6kgdry/kgH2capacity. Do not normalize126kgmaterial to10kgdrytank. Stationinstalledcapacity125kgH2 fromS8,20yearvessellife and40yearstationlife implytwo manufacturedsets inone40yearstationinventory,not two125kgvesselsinstalledandthenanotherreplacementfactor. Newunitprovider is one125kgH2capacity installedtankreference containing1575kgdrymaterial,includingits existingtankBoPproportions; sourcepressure,individualcylindercount andcertification unspecified,not labelled700barorbusType4without evidence. Stationbuystwounits total250kgH2capacity manufacture/3150kgdry overlife,exactlypreservingoriginalmaterial,processenergyandformingvectors afterissue70. No hiddennewrecyclingcredit,treatmentorsecondlifetime divisor; originalstationgenericEOLgap remains. Theoriginalkgprovider remainsavailableaslegacycapacityreference withclarifiedcomment,soexternalconsumers donot silently changefunctionalunit. Newexplicitunitprovider is activeforstationonly. Cylinderpressure/reserve/actualhydrogenusablefraction anddemandutilization arestillengineeringgaps. Existing850kg/daynameplate,70%utilization,595kg/dayhydrogen throughput and40yearserviceallocation are unchanged; no operationalcompression/precooling change. Neither3160kgwetmassnorstoredhydrogenfeed ismanufacturedmetal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>hydrogen storage tank system, station125kg H2 capacity, engineering reference</t>
+        </is>
+      </c>
+      <c r="B376">
+        <v>1</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>hydrogen storage tank system, station125kg H2 capacity, engineering reference</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>hydrogen storage tank system, station125kg H2 capacity, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="B377">
+        <v>75.0</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B378">
+        <v>75.0</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, chromium steel</t>
+        </is>
+      </c>
+      <c r="B379">
+        <v>112.5</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>sheet rolling, chromium steel</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>sheet rolling, chromium steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>market for steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="B380">
+        <v>112.5</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>carbon fiber production, weaved, at factory</t>
+        </is>
+      </c>
+      <c r="B381">
+        <v>892.5000000000001</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>carbon fiber, weaved</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>carbon fiber, weaved</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B382">
+        <v>382.5</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>market group for electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="B383">
+        <v>56.25</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>electricity, low voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, steel</t>
+        </is>
+      </c>
+      <c r="B384">
+        <v>112.5</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>sheet rolling, steel</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>sheet rolling, steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B385">
+        <v>112.5</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I365" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
@@ -1231,7 +1231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T385"/>
+  <dimension ref="A1:T440"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44.5" customWidth="1"/>
@@ -3906,8 +3906,23 @@
       <c r="A104" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B104" s="8" t="s">
-        <v>201</v>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED EXPLICIT GALVALUME METAL FEED, issue72,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook. Introducea clearlydefined1kgretainedGalvalume coatingreference with0.55kgAl,0.434kgZn,0.016kgSi. Itisnot1kgpureZn,nor1kgcoatedsteel,andsodaashcannotprovideZn. UsegenericwroughtAl,marketZn andmetallurgicalSisupply; forming/galvanicalloying1kWh/kg explicitengineeringassemblyallowance.95%metalretention reference,test90-100%;grossfeeds=retained/.95,pairedmixedmanufacturingwaste=(1/.95-1)kgminusdeclaredZnrelease2.94e-5kg. DetailedZn/Al/Si-specificlossfatesunresolved; donot countallscrapasrecoverablemetal. Copyotherexistingpublicbathchemical/utility/emissionprocess coefficients as a DOCUMENTEDPROXY,not verifiedmodernapplicationdata. Inparticularretain1kgsodaash/kgcoatingconservatively becausetheoriginalWulfS3explicitlysays1000kg/tonne; thereisnosourcedbasis to silentlyreplaceitbyZn ordeletea potentialbathchemical. Thisanomalouschemicalintensity remains a quantified sourcegap,not a closedindustrialrecipe. HeatCHPunit/source dust-factor anomalies arelikewiseunresolvedinexistingprocessreference; no fullprocesscertification. Thusnumericalmetalfeedisnowexplicitwhileuncertainnonmetalprocessburdensremainvisible. ExistingZn/othertraceemissionsretainedfromsource;subtractZnreleasefrommatchednetmetallosswasteforno doublemetal-lossaccount. Thisdoesnotbalanceunmeasuredtraceelementsinbathchemicals. No globalnativegalvanizingedit. Rewirebothpipelineconstructioncoatingpurchases tothis1kgfinishedcoatingprovider atunchanged446.05kg/km inthiscommit; issue73 separatelycorrects geometricdose andpolymer/lifecycleboundary. Originallegacycoatingprovider retainedforcompatibility andannotatedwithknownsourceproblem. ActualpipelineGalvalumegrade isdocumented55/43.4/1.6; layerthicknessandcoatedarea addressednext. Noassumedzerozincor unsupportedcredit.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+LCI of 1 km of distribution pipeline, source from C. Tsiklios, M. Hermesmann, T.E. Müller, Hydrogen transport in large-scale distribution pipeline networks: Thermodynamic and environmental assessment of repurposed and new pipeline configurations, Applied Energy, 2022, https://doi.org/10.1016/j.apenergy.2022.120097.
+distribution pipeline
+Lifetime [years]: 40
+Operating pressure range [bar]: 16-100, 80 as reference
+Annual operating hours [hours]: 8,000
+Hydrogen circulated per lifetime [Mt]: 124.81
+Mass flow [kg/s]: 108.34
+Outer diameter [m]: 1.22
+Inner coating layer [micro-m]: 65
+Steel layer [mm]: 27.09
+Epoxy resin layer [mm]: 0.15
+HDPE layer [mm]: 3</t>
+        </is>
       </c>
       <c r="K104" s="9"/>
       <c r="L104" s="9"/>
@@ -4259,14 +4274,18 @@
       </c>
     </row>
     <row r="113" spans="1:20" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A113" s="8" t="s">
-        <v>72</v>
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+        </is>
       </c>
       <c r="B113" s="8">
         <v>446.05</v>
       </c>
-      <c r="C113" s="8" t="s">
-        <v>41</v>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D113" s="8" t="s">
         <v>21</v>
@@ -4274,8 +4293,10 @@
       <c r="F113" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G113" s="8" t="s">
-        <v>72</v>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+        </is>
       </c>
       <c r="H113" s="8" t="s">
         <v>205</v>
@@ -5300,8 +5321,23 @@
       <c r="A153" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B153" s="8" t="s">
-        <v>219</v>
+      <c r="B153" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED EXPLICIT GALVALUME METAL FEED, issue72,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook. Introducea clearlydefined1kgretainedGalvalume coatingreference with0.55kgAl,0.434kgZn,0.016kgSi. Itisnot1kgpureZn,nor1kgcoatedsteel,andsodaashcannotprovideZn. UsegenericwroughtAl,marketZn andmetallurgicalSisupply; forming/galvanicalloying1kWh/kg explicitengineeringassemblyallowance.95%metalretention reference,test90-100%;grossfeeds=retained/.95,pairedmixedmanufacturingwaste=(1/.95-1)kgminusdeclaredZnrelease2.94e-5kg. DetailedZn/Al/Si-specificlossfatesunresolved; donot countallscrapasrecoverablemetal. Copyotherexistingpublicbathchemical/utility/emissionprocess coefficients as a DOCUMENTEDPROXY,not verifiedmodernapplicationdata. Inparticularretain1kgsodaash/kgcoatingconservatively becausetheoriginalWulfS3explicitlysays1000kg/tonne; thereisnosourcedbasis to silentlyreplaceitbyZn ordeletea potentialbathchemical. Thisanomalouschemicalintensity remains a quantified sourcegap,not a closedindustrialrecipe. HeatCHPunit/source dust-factor anomalies arelikewiseunresolvedinexistingprocessreference; no fullprocesscertification. Thusnumericalmetalfeedisnowexplicitwhileuncertainnonmetalprocessburdensremainvisible. ExistingZn/othertraceemissionsretainedfromsource;subtractZnreleasefrommatchednetmetallosswasteforno doublemetal-lossaccount. Thisdoesnotbalanceunmeasuredtraceelementsinbathchemicals. No globalnativegalvanizingedit. Rewirebothpipelineconstructioncoatingpurchases tothis1kgfinishedcoatingprovider atunchanged446.05kg/km inthiscommit; issue73 separatelycorrects geometricdose andpolymer/lifecycleboundary. Originallegacycoatingprovider retainedforcompatibility andannotatedwithknownsourceproblem. ActualpipelineGalvalumegrade isdocumented55/43.4/1.6; layerthicknessandcoatedarea addressednext. Noassumedzerozincor unsupportedcredit.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+LCI of 1 km of transmission pipeline, source from C. Tsiklios, M. Hermesmann, T.E. Müller, Hydrogen transport in large-scale transmission pipeline networks: Thermodynamic and environmental assessment of repurposed and new pipeline configurations, Applied Energy, 2022, https://doi.org/10.1016/j.apenergy.2022.120097.
+Transmission pipeline
+Lifetime [years]: 40
+Operating pressure range [bar]: 16-100, 80 as reference
+Annual operating hours [hours]: 8,000
+Hydrogen circulated per lifetime [Mt]: 124.81
+Mass flow [kg/s]: 108.34
+Outer diameter [m]: 1.22
+Inner coating layer [micro-m]: 65
+Steel layer [mm]: 27.09
+Epoxy resin layer [mm]: 0.15
+HDPE layer [mm]: 3</t>
+        </is>
       </c>
       <c r="K153" s="9"/>
       <c r="L153" s="9"/>
@@ -5653,14 +5689,18 @@
       </c>
     </row>
     <row r="162" spans="1:20" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A162" s="8" t="s">
-        <v>72</v>
+      <c r="A162" s="8" t="inlineStr">
+        <is>
+          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+        </is>
       </c>
       <c r="B162" s="8">
         <v>446.05</v>
       </c>
-      <c r="C162" s="8" t="s">
-        <v>41</v>
+      <c r="C162" s="8" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D162" s="8" t="s">
         <v>21</v>
@@ -5668,8 +5708,10 @@
       <c r="F162" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G162" s="8" t="s">
-        <v>72</v>
+      <c r="G162" s="8" t="inlineStr">
+        <is>
+          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+        </is>
       </c>
       <c r="H162" s="8" t="s">
         <v>205</v>
@@ -6694,8 +6736,12 @@
       <c r="A202" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B202" s="8" t="s">
-        <v>153</v>
+      <c r="B202" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED EXPLICIT GALVALUME METAL FEED, issue72,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook. Introducea clearlydefined1kgretainedGalvalume coatingreference with0.55kgAl,0.434kgZn,0.016kgSi. Itisnot1kgpureZn,nor1kgcoatedsteel,andsodaashcannotprovideZn. UsegenericwroughtAl,marketZn andmetallurgicalSisupply; forming/galvanicalloying1kWh/kg explicitengineeringassemblyallowance.95%metalretention reference,test90-100%;grossfeeds=retained/.95,pairedmixedmanufacturingwaste=(1/.95-1)kgminusdeclaredZnrelease2.94e-5kg. DetailedZn/Al/Si-specificlossfatesunresolved; donot countallscrapasrecoverablemetal. Copyotherexistingpublicbathchemical/utility/emissionprocess coefficients as a DOCUMENTEDPROXY,not verifiedmodernapplicationdata. Inparticularretain1kgsodaash/kgcoatingconservatively becausetheoriginalWulfS3explicitlysays1000kg/tonne; thereisnosourcedbasis to silentlyreplaceitbyZn ordeletea potentialbathchemical. Thisanomalouschemicalintensity remains a quantified sourcegap,not a closedindustrialrecipe. HeatCHPunit/source dust-factor anomalies arelikewiseunresolvedinexistingprocessreference; no fullprocesscertification. Thusnumericalmetalfeedisnowexplicitwhileuncertainnonmetalprocessburdensremainvisible. ExistingZn/othertraceemissionsretainedfromsource;subtractZnreleasefrommatchednetmetallosswasteforno doublemetal-lossaccount. Thisdoesnotbalanceunmeasuredtraceelementsinbathchemicals. No globalnativegalvanizingedit. Rewirebothpipelineconstructioncoatingpurchases tothis1kgfinishedcoatingprovider atunchanged446.05kg/km inthiscommit; issue73 separatelycorrects geometricdose andpolymer/lifecycleboundary. Originallegacycoatingprovider retainedforcompatibility andannotatedwithknownsourceproblem. ActualpipelineGalvalumegrade isdocumented55/43.4/1.6; layerthicknessandcoatedarea addressednext. Noassumedzerozincor unsupportedcredit.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+LCI of the process of applying 1 kg of zinc coating (Faist Emmenegger et al., 2007a, b; Krieg, 2012)</t>
+        </is>
       </c>
       <c r="K202" s="9"/>
       <c r="L202" s="9"/>
@@ -11607,6 +11653,1572 @@
         </is>
       </c>
     </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>APPROVED EXPLICIT GALVALUME METAL FEED, issue72,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook. Introducea clearlydefined1kgretainedGalvalume coatingreference with0.55kgAl,0.434kgZn,0.016kgSi. Itisnot1kgpureZn,nor1kgcoatedsteel,andsodaashcannotprovideZn. UsegenericwroughtAl,marketZn andmetallurgicalSisupply; forming/galvanicalloying1kWh/kg explicitengineeringassemblyallowance.95%metalretention reference,test90-100%;grossfeeds=retained/.95,pairedmixedmanufacturingwaste=(1/.95-1)kgminusdeclaredZnrelease2.94e-5kg. DetailedZn/Al/Si-specificlossfatesunresolved; donot countallscrapasrecoverablemetal. Copyotherexistingpublicbathchemical/utility/emissionprocess coefficients as a DOCUMENTEDPROXY,not verifiedmodernapplicationdata. Inparticularretain1kgsodaash/kgcoatingconservatively becausetheoriginalWulfS3explicitlysays1000kg/tonne; thereisnosourcedbasis to silentlyreplaceitbyZn ordeletea potentialbathchemical. Thisanomalouschemicalintensity remains a quantified sourcegap,not a closedindustrialrecipe. HeatCHPunit/source dust-factor anomalies arelikewiseunresolvedinexistingprocessreference; no fullprocesscertification. Thusnumericalmetalfeedisnowexplicitwhileuncertainnonmetalprocessburdensremainvisible. ExistingZn/othertraceemissionsretainedfromsource;subtractZnreleasefrommatchednetmetallosswasteforno doublemetal-lossaccount. Thisdoesnotbalanceunmeasuredtraceelementsinbathchemicals. No globalnativegalvanizingedit. Rewirebothpipelineconstructioncoatingpurchases tothis1kgfinishedcoatingprovider atunchanged446.05kg/km inthiscommit; issue73 separatelycorrects geometricdose andpolymer/lifecycleboundary. Originallegacycoatingprovider retainedforcompatibility andannotatedwithknownsourceproblem. ActualpipelineGalvalumegrade isdocumented55/43.4/1.6; layerthicknessandcoatedarea addressednext. Noassumedzerozincor unsupportedcredit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+        </is>
+      </c>
+      <c r="B397">
+        <v>1</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B398">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>market for zinc</t>
+        </is>
+      </c>
+      <c r="B399">
+        <v>0.45684210526315794</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>market for silicon, metallurgical grade</t>
+        </is>
+      </c>
+      <c r="B400">
+        <v>0.016842105263157894</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>silicon, metallurgical grade</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>silicon, metallurgical grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>market for electric arc furnace dust</t>
+        </is>
+      </c>
+      <c r="B401">
+        <v>-1.4e-05</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>electric arc furnace dust</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>electric arc furnace dust</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>treatment of waste mineral oil, hazardous waste incineration</t>
+        </is>
+      </c>
+      <c r="B402">
+        <v>-0.00016</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>waste mineral oil</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>waste mineral oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>market for sludge from steel rolling</t>
+        </is>
+      </c>
+      <c r="B403">
+        <v>-9.06e-05</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>sludge from steel rolling</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>sludge from steel rolling</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B404">
+        <v>0.2</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>market for chemicals, inorganic</t>
+        </is>
+      </c>
+      <c r="B405">
+        <v>0.0015</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>chemical, inorganic</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>chemical, inorganic</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>market for aluminium sulfate, powder</t>
+        </is>
+      </c>
+      <c r="B406">
+        <v>9.06e-07</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>aluminium sulfate, powder</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>aluminium sulfate, powder</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>market for ammonia, anhydrous, liquid</t>
+        </is>
+      </c>
+      <c r="B407">
+        <v>3.5999999999999994e-05</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>ammonia, anhydrous, liquid</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>ammonia, anhydrous, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>heat production, light fuel oil, at boiler 100kW, non-modulating</t>
+        </is>
+      </c>
+      <c r="B408">
+        <v>0.768</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>heat, central or small-scale, other than natural gas</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>heat, central or small-scale, other than natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>market for heat, from steam, in chemical industry</t>
+        </is>
+      </c>
+      <c r="B409">
+        <v>0.0201</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>heat, from steam, in chemical industry</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>heat, from steam, in chemical industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>market for hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+      <c r="B410">
+        <v>0.0222</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>market for heat, central or small-scale, natural gas</t>
+        </is>
+      </c>
+      <c r="B411">
+        <v>0.768</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>heat, central or small-scale, natural gas</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>heat, central or small-scale, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>market for rolling mill</t>
+        </is>
+      </c>
+      <c r="B412">
+        <v>1.63e-13</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>rolling mill</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>rolling mill</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>market for soda ash, light, crystalline, heptahydrate</t>
+        </is>
+      </c>
+      <c r="B413">
+        <v>1</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>soda ash, light, crystalline, heptahydrate</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>soda ash, light, crystalline, heptahydrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>market for sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+      <c r="B414">
+        <v>0.00038</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>market for transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="B415">
+        <v>0.008039999999999999</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>market group for electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="B416">
+        <v>0.02033333333333333</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>electricity, low voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B417">
+        <v>-0.052602178947368364</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B418">
+        <v>1</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Ammonia</t>
+        </is>
+      </c>
+      <c r="B419">
+        <v>4.36e-05</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Arsenic ion</t>
+        </is>
+      </c>
+      <c r="B420">
+        <v>1.9000000000000002e-10</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>BOD5, Biological Oxygen Demand</t>
+        </is>
+      </c>
+      <c r="B421">
+        <v>1.32e-05</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>water::ground-</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Cadmium II</t>
+        </is>
+      </c>
+      <c r="B422">
+        <v>1.31e-09</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>COD, Chemical Oxygen Demand</t>
+        </is>
+      </c>
+      <c r="B423">
+        <v>0.000132</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>water::ground-</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Chloride</t>
+        </is>
+      </c>
+      <c r="B424">
+        <v>1.88e-06</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>water::ground-</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Chromium VI</t>
+        </is>
+      </c>
+      <c r="B425">
+        <v>7.6e-09</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>water::ground-</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Particulate Matter, &gt; 10 um</t>
+        </is>
+      </c>
+      <c r="B426">
+        <v>0.000157</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Particulate Matter, &gt; 2.5 um and &lt; 10um</t>
+        </is>
+      </c>
+      <c r="B427">
+        <v>0.00762</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Hydrocarbons, unspecified</t>
+        </is>
+      </c>
+      <c r="B428">
+        <v>1.1900000000000001e-07</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>water::ground-</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Hydrochloric acid</t>
+        </is>
+      </c>
+      <c r="B429">
+        <v>1.83e-05</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Iron ion</t>
+        </is>
+      </c>
+      <c r="B430">
+        <v>1.4e-06</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Iron ion</t>
+        </is>
+      </c>
+      <c r="B431">
+        <v>5.649999999999999e-06</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>water::ground-</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Lead II</t>
+        </is>
+      </c>
+      <c r="B432">
+        <v>3.4000000000000003e-09</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Lead II</t>
+        </is>
+      </c>
+      <c r="B433">
+        <v>1.51e-09</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>water::ground-</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Nickel II</t>
+        </is>
+      </c>
+      <c r="B434">
+        <v>9.999999999999999e-10</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>water::ground-</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Oils, unspecified</t>
+        </is>
+      </c>
+      <c r="B435">
+        <v>1.0399999999999999e-07</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>water::ground-</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Phosphorus</t>
+        </is>
+      </c>
+      <c r="B436">
+        <v>9.000000000000001e-08</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>water::ground-</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Suspended solids, unspecified</t>
+        </is>
+      </c>
+      <c r="B437">
+        <v>2.24e-07</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>water::ground-</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>TOC, Total Organic Carbon</t>
+        </is>
+      </c>
+      <c r="B438">
+        <v>2.97e-07</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>water::ground-</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Zinc II</t>
+        </is>
+      </c>
+      <c r="B439">
+        <v>2.75e-05</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Zinc II</t>
+        </is>
+      </c>
+      <c r="B440">
+        <v>1.9e-06</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>water::ground-</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I365" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
@@ -1231,7 +1231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T440"/>
+  <dimension ref="A1:T454"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44.5" customWidth="1"/>
@@ -2119,8 +2119,10 @@
       <c r="A54" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B54" s="8" t="s">
-        <v>163</v>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED HYDROGEN PIPELINE GEOMETRY AND MATERIAL BOUNDARY, issue73,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly. Distribution selection is an explicit engineering adaptation,not an independently pressure-certified19bar pipeline:OD105mm,ID100mm=&gt;wall2.5mm,not copied4.5mm or27.09*(5/55). Steel density7850kg/m3 gives6319.509972236697kg/km; buy steel material AND equal pipe-drawing service,not two steel material inputs. Galvalume retainedmass=innerarea*pi*ID*length*65um*alloydensity; idealvolume-additive density=1/(.55/2700+.434/7140+.016/2330)=3685.2098164751933kg/m3. Transmission innerarea3660m2 fromsource gives876.7114153394484kg/km; distribution innerarea314.159m2 gives75.25328256144047kg/km. Thickness65um and idealalloydensity are explicitreferencechoices; actualmeasuredcoatingdensity/roughness/porosity need verification,test thickness30-100um. SourceGalvalume is reportedm2,notkg:original446.05kg cannot be transferred unchangedacrossdiameters. Both now buy issue72kgretainedalloy provider; its95%metalyield and unresolvedsodaash/processanomalies remainvisible. HDPEannulus outside25umFBE and0.5mmHDPE at950kg/m3 gives157.50767467854035kg/km; feedfullHDPEgranulateandmatchingextrusionservice,notextrusiononly. Transmission5599.17kgHDPE retainedassourced,not rederived underdistributiongeometry. NewHDPEprovider100%retentionreference,processscrap/yieldgapexplicit,test95-100%; no inventednegativeplasticcredit. Powdercoating native reference documents80um architecturalpowder,NOT source-specificFBE:purchase actualouterarea*selectedthickness/80um (25distribution,150transmission). This is an explicit thickness-proportional equivalent-area proxy including utilities; actualFBEresin/hardener,curingenergyperarea andservice-life gaps remain,not claimed industrialFBEreconstruction. Neither the addedHDPEfeed nor the coatservice includessteelmaterial. Freightretainseachoriginalimpliedmass-distance route for steel+Galvalume+HDPE,updatingtkmfornewretainedmass; excludesunknownpowder-retainedmass/sandfreight,asbefore. Distributiontrenchvolumes,sand,landuse/water andhelicoptersremainexistingperkmreferences ratherthan blindlyscaledbydiameteror100; trenchwidth andactualinstallationneedfieldvalidation. Service40years/0.22MtH2 and19bar distributionassumption retained,hydraulicsnotrecalculated; transmission40years/124.81Mtandcompressor125kmspacing unchanged. Treatment alreadyhas -1kmproduction andwrapper-1kmwasteinput:correctsigns preserved,not invertedorduplicated. Retainexisting50%landfill/treatment scenario as engineeringboundary,nowhalfretainedsteel+Galvalumemass toexistingdecommissionedpipeline treatment andhalfHDPE toexistingplastic treatment. Otherhalfmetal/polymerfate andpowdercoatingtreatment remainunresolved; no assumedprimary-secondaryshare,recoverycreditorclaimofcompleteEOLcoverage. Genericpipelinewastetreatment maycontainits ownlegacycomposition; not element-specificGalvalume recovery. Correctonlymisleadingdistributionmetadata; nativeprocesses/runtime/YAML unchanged. Geometry-derivedquantities:{'steel_kg_per_km': 6319.509972236697, 'Galvalume_kg_per_km': 75.25328256144047, 'HDPE_kg_per_km': 157.50767467854035}.</t>
+        </is>
       </c>
       <c r="K54" s="9"/>
       <c r="L54" s="9"/>
@@ -3017,8 +3019,12 @@
       <c r="A79" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B79" s="8" t="s">
-        <v>196</v>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED HYDROGEN PIPELINE GEOMETRY AND MATERIAL BOUNDARY, issue73,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly. Distribution selection is an explicit engineering adaptation,not an independently pressure-certified19bar pipeline:OD105mm,ID100mm=&gt;wall2.5mm,not copied4.5mm or27.09*(5/55). Steel density7850kg/m3 gives6319.509972236697kg/km; buy steel material AND equal pipe-drawing service,not two steel material inputs. Galvalume retainedmass=innerarea*pi*ID*length*65um*alloydensity; idealvolume-additive density=1/(.55/2700+.434/7140+.016/2330)=3685.2098164751933kg/m3. Transmission innerarea3660m2 fromsource gives876.7114153394484kg/km; distribution innerarea314.159m2 gives75.25328256144047kg/km. Thickness65um and idealalloydensity are explicitreferencechoices; actualmeasuredcoatingdensity/roughness/porosity need verification,test thickness30-100um. SourceGalvalume is reportedm2,notkg:original446.05kg cannot be transferred unchangedacrossdiameters. Both now buy issue72kgretainedalloy provider; its95%metalyield and unresolvedsodaash/processanomalies remainvisible. HDPEannulus outside25umFBE and0.5mmHDPE at950kg/m3 gives157.50767467854035kg/km; feedfullHDPEgranulateandmatchingextrusionservice,notextrusiononly. Transmission5599.17kgHDPE retainedassourced,not rederived underdistributiongeometry. NewHDPEprovider100%retentionreference,processscrap/yieldgapexplicit,test95-100%; no inventednegativeplasticcredit. Powdercoating native reference documents80um architecturalpowder,NOT source-specificFBE:purchase actualouterarea*selectedthickness/80um (25distribution,150transmission). This is an explicit thickness-proportional equivalent-area proxy including utilities; actualFBEresin/hardener,curingenergyperarea andservice-life gaps remain,not claimed industrialFBEreconstruction. Neither the addedHDPEfeed nor the coatservice includessteelmaterial. Freightretainseachoriginalimpliedmass-distance route for steel+Galvalume+HDPE,updatingtkmfornewretainedmass; excludesunknownpowder-retainedmass/sandfreight,asbefore. Distributiontrenchvolumes,sand,landuse/water andhelicoptersremainexistingperkmreferences ratherthan blindlyscaledbydiameteror100; trenchwidth andactualinstallationneedfieldvalidation. Service40years/0.22MtH2 and19bar distributionassumption retained,hydraulicsnotrecalculated; transmission40years/124.81Mtandcompressor125kmspacing unchanged. Treatment alreadyhas -1kmproduction andwrapper-1kmwasteinput:correctsigns preserved,not invertedorduplicated. Retainexisting50%landfill/treatment scenario as engineeringboundary,nowhalfretainedsteel+Galvalumemass toexistingdecommissionedpipeline treatment andhalfHDPE toexistingplastic treatment. Otherhalfmetal/polymerfate andpowdercoatingtreatment remainunresolved; no assumedprimary-secondaryshare,recoverycreditorclaimofcompleteEOLcoverage. Genericpipelinewastetreatment maycontainits ownlegacycomposition; not element-specificGalvalume recovery. Correctonlymisleadingdistributionmetadata; nativeprocesses/runtime/YAML unchanged. Geometry-derivedquantities:{'steel_kg_per_km': 6319.509972236697, 'Galvalume_kg_per_km': 75.25328256144047, 'HDPE_kg_per_km': 157.50767467854035}.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+LCI of 1 km of transmission pipeline, source from C. Tsiklios, M. Hermesmann, T.E. Müller, Hydrogen transport in large-scale transmission pipeline networks: Thermodynamic and environmental assessment of repurposed and new pipeline configurations, Applied Energy, 2022, https://doi.org/10.1016/j.apenergy.2022.120097. Lifetime [years]: 40, Operating pressure range [bar]: 16-100, 80 as reference, Annual operating hours [hours]: 8,000, Hydrogen circulated per lifetime [Mt]: 124.81, Mass flow [kg/s]: 108.34, Outer diameter [m]: 1.22, Inner coating layer [micro-m]: 65, Steel layer [mm]: 27.09, Epoxy resin layer [mm]: 0.15: HDPE layer [mm]: 3.</t>
+        </is>
       </c>
       <c r="K79" s="9"/>
       <c r="L79" s="9"/>
@@ -3908,20 +3914,7 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>APPROVED EXPLICIT GALVALUME METAL FEED, issue72,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook. Introducea clearlydefined1kgretainedGalvalume coatingreference with0.55kgAl,0.434kgZn,0.016kgSi. Itisnot1kgpureZn,nor1kgcoatedsteel,andsodaashcannotprovideZn. UsegenericwroughtAl,marketZn andmetallurgicalSisupply; forming/galvanicalloying1kWh/kg explicitengineeringassemblyallowance.95%metalretention reference,test90-100%;grossfeeds=retained/.95,pairedmixedmanufacturingwaste=(1/.95-1)kgminusdeclaredZnrelease2.94e-5kg. DetailedZn/Al/Si-specificlossfatesunresolved; donot countallscrapasrecoverablemetal. Copyotherexistingpublicbathchemical/utility/emissionprocess coefficients as a DOCUMENTEDPROXY,not verifiedmodernapplicationdata. Inparticularretain1kgsodaash/kgcoatingconservatively becausetheoriginalWulfS3explicitlysays1000kg/tonne; thereisnosourcedbasis to silentlyreplaceitbyZn ordeletea potentialbathchemical. Thisanomalouschemicalintensity remains a quantified sourcegap,not a closedindustrialrecipe. HeatCHPunit/source dust-factor anomalies arelikewiseunresolvedinexistingprocessreference; no fullprocesscertification. Thusnumericalmetalfeedisnowexplicitwhileuncertainnonmetalprocessburdensremainvisible. ExistingZn/othertraceemissionsretainedfromsource;subtractZnreleasefrommatchednetmetallosswasteforno doublemetal-lossaccount. Thisdoesnotbalanceunmeasuredtraceelementsinbathchemicals. No globalnativegalvanizingedit. Rewirebothpipelineconstructioncoatingpurchases tothis1kgfinishedcoatingprovider atunchanged446.05kg/km inthiscommit; issue73 separatelycorrects geometricdose andpolymer/lifecycleboundary. Originallegacycoatingprovider retainedforcompatibility andannotatedwithknownsourceproblem. ActualpipelineGalvalumegrade isdocumented55/43.4/1.6; layerthicknessandcoatedarea addressednext. Noassumedzerozincor unsupportedcredit.
-PREVIOUS NOTES (retained as history; the correction above takes precedence):
-LCI of 1 km of distribution pipeline, source from C. Tsiklios, M. Hermesmann, T.E. Müller, Hydrogen transport in large-scale distribution pipeline networks: Thermodynamic and environmental assessment of repurposed and new pipeline configurations, Applied Energy, 2022, https://doi.org/10.1016/j.apenergy.2022.120097.
-distribution pipeline
-Lifetime [years]: 40
-Operating pressure range [bar]: 16-100, 80 as reference
-Annual operating hours [hours]: 8,000
-Hydrogen circulated per lifetime [Mt]: 124.81
-Mass flow [kg/s]: 108.34
-Outer diameter [m]: 1.22
-Inner coating layer [micro-m]: 65
-Steel layer [mm]: 27.09
-Epoxy resin layer [mm]: 0.15
-HDPE layer [mm]: 3</t>
+          <t>APPROVED HYDROGEN PIPELINE GEOMETRY AND MATERIAL BOUNDARY, issue73,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly. Distribution selection is an explicit engineering adaptation,not an independently pressure-certified19bar pipeline:OD105mm,ID100mm=&gt;wall2.5mm,not copied4.5mm or27.09*(5/55). Steel density7850kg/m3 gives6319.509972236697kg/km; buy steel material AND equal pipe-drawing service,not two steel material inputs. Galvalume retainedmass=innerarea*pi*ID*length*65um*alloydensity; idealvolume-additive density=1/(.55/2700+.434/7140+.016/2330)=3685.2098164751933kg/m3. Transmission innerarea3660m2 fromsource gives876.7114153394484kg/km; distribution innerarea314.159m2 gives75.25328256144047kg/km. Thickness65um and idealalloydensity are explicitreferencechoices; actualmeasuredcoatingdensity/roughness/porosity need verification,test thickness30-100um. SourceGalvalume is reportedm2,notkg:original446.05kg cannot be transferred unchangedacrossdiameters. Both now buy issue72kgretainedalloy provider; its95%metalyield and unresolvedsodaash/processanomalies remainvisible. HDPEannulus outside25umFBE and0.5mmHDPE at950kg/m3 gives157.50767467854035kg/km; feedfullHDPEgranulateandmatchingextrusionservice,notextrusiononly. Transmission5599.17kgHDPE retainedassourced,not rederived underdistributiongeometry. NewHDPEprovider100%retentionreference,processscrap/yieldgapexplicit,test95-100%; no inventednegativeplasticcredit. Powdercoating native reference documents80um architecturalpowder,NOT source-specificFBE:purchase actualouterarea*selectedthickness/80um (25distribution,150transmission). This is an explicit thickness-proportional equivalent-area proxy including utilities; actualFBEresin/hardener,curingenergyperarea andservice-life gaps remain,not claimed industrialFBEreconstruction. Neither the addedHDPEfeed nor the coatservice includessteelmaterial. Freightretainseachoriginalimpliedmass-distance route for steel+Galvalume+HDPE,updatingtkmfornewretainedmass; excludesunknownpowder-retainedmass/sandfreight,asbefore. Distributiontrenchvolumes,sand,landuse/water andhelicoptersremainexistingperkmreferences ratherthan blindlyscaledbydiameteror100; trenchwidth andactualinstallationneedfieldvalidation. Service40years/0.22MtH2 and19bar distributionassumption retained,hydraulicsnotrecalculated; transmission40years/124.81Mtandcompressor125kmspacing unchanged. Treatment alreadyhas -1kmproduction andwrapper-1kmwasteinput:correctsigns preserved,not invertedorduplicated. Retainexisting50%landfill/treatment scenario as engineeringboundary,nowhalfretainedsteel+Galvalumemass toexistingdecommissionedpipeline treatment andhalfHDPE toexistingplastic treatment. Otherhalfmetal/polymerfate andpowdercoatingtreatment remainunresolved; no assumedprimary-secondaryshare,recoverycreditorclaimofcompleteEOLcoverage. Genericpipelinewastetreatment maycontainits ownlegacycomposition; not element-specificGalvalume recovery. Correctonlymisleadingdistributionmetadata; nativeprocesses/runtime/YAML unchanged. Geometry-derivedquantities:{'steel_kg_per_km': 6319.509972236697, 'Galvalume_kg_per_km': 75.25328256144047, 'HDPE_kg_per_km': 157.50767467854035}.</t>
         </is>
       </c>
       <c r="K104" s="9"/>
@@ -4069,7 +4062,7 @@
         <v>2</v>
       </c>
       <c r="J109">
-        <f t="shared" ref="J109:J115" si="6">LN(B109)</f>
+        <f>LN(B109)</f>
         <v>-6.2146080984221914</v>
       </c>
       <c r="K109" s="6">
@@ -4094,7 +4087,7 @@
         <v>3</v>
       </c>
       <c r="R109">
-        <f t="shared" ref="R109:R115" si="7">LN(SQRT(EXP(
+        <f>LN(SQRT(EXP(
 SQRT(
 +POWER(LN(K109),2)
 +POWER(LN(L109),2)
@@ -4134,7 +4127,7 @@
         <v>2</v>
       </c>
       <c r="J110">
-        <f t="shared" si="6"/>
+        <f>LN(B110)</f>
         <v>-1.8325814637483102</v>
       </c>
       <c r="K110" s="6">
@@ -4159,7 +4152,17 @@
         <v>3</v>
       </c>
       <c r="R110">
-        <f t="shared" si="7"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K110),2)
++POWER(LN(L110),2)
++POWER(LN(M110),2)
++POWER(LN(N110),2)
++POWER(LN(O110),2)
++POWER(LN(P110),2)
++POWER(LN(Q110),2)
+)
+)))</f>
         <v>0.72314801614797197</v>
       </c>
     </row>
@@ -4168,7 +4171,7 @@
         <v>208</v>
       </c>
       <c r="B111" s="14">
-        <v>7914.4736000000003</v>
+        <v>6319.509972236697</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>2</v>
@@ -4189,8 +4192,8 @@
         <v>2</v>
       </c>
       <c r="J111">
-        <f t="shared" si="6"/>
-        <v>8.9764484634704722</v>
+        <f>8.751396948096332</f>
+        <v>8.751396948096332</v>
       </c>
       <c r="K111" s="6">
         <v>1.5</v>
@@ -4214,7 +4217,17 @@
         <v>2</v>
       </c>
       <c r="R111">
-        <f t="shared" si="7"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K111),2)
++POWER(LN(L111),2)
++POWER(LN(M111),2)
++POWER(LN(N111),2)
++POWER(LN(O111),2)
++POWER(LN(P111),2)
++POWER(LN(Q111),2)
+)
+)))</f>
         <v>0.58422518478336083</v>
       </c>
     </row>
@@ -4223,7 +4236,7 @@
         <v>209</v>
       </c>
       <c r="B112" s="14">
-        <v>38.302300000000002</v>
+        <v>103.08350894591509</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>41</v>
@@ -4244,8 +4257,8 @@
         <v>2</v>
       </c>
       <c r="J112">
-        <f t="shared" si="6"/>
-        <v>3.6455099466028593</v>
+        <f>4.635539426201243</f>
+        <v>4.635539426201243</v>
       </c>
       <c r="K112" s="6">
         <v>1.5</v>
@@ -4269,7 +4282,17 @@
         <v>2</v>
       </c>
       <c r="R112">
-        <f t="shared" si="7"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K112),2)
++POWER(LN(L112),2)
++POWER(LN(M112),2)
++POWER(LN(N112),2)
++POWER(LN(O112),2)
++POWER(LN(P112),2)
++POWER(LN(Q112),2)
+)
+)))</f>
         <v>0.58422518478336083</v>
       </c>
     </row>
@@ -4280,7 +4303,7 @@
         </is>
       </c>
       <c r="B113" s="8">
-        <v>446.05</v>
+        <v>75.25328256144047</v>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
@@ -4305,8 +4328,8 @@
         <v>2</v>
       </c>
       <c r="J113">
-        <f t="shared" si="6"/>
-        <v>6.1004310533597925</v>
+        <f>4.320859524756513</f>
+        <v>4.320859524756513</v>
       </c>
       <c r="K113" s="6">
         <v>1.5</v>
@@ -4330,28 +4353,46 @@
         <v>2</v>
       </c>
       <c r="R113">
-        <f t="shared" si="7"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K113),2)
++POWER(LN(L113),2)
++POWER(LN(M113),2)
++POWER(LN(N113),2)
++POWER(LN(O113),2)
++POWER(LN(P113),2)
++POWER(LN(Q113),2)
+)
+)))</f>
         <v>0.58422518478336083</v>
       </c>
     </row>
     <row r="114" spans="1:20" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A114" s="13" t="s">
-        <v>211</v>
+      <c r="A114" s="13" t="inlineStr">
+        <is>
+          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+        </is>
       </c>
       <c r="B114" s="14">
-        <v>55.991700000000002</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>21</v>
+        <v>157.50767467854035</v>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
       </c>
       <c r="F114" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G114" s="13" t="s">
-        <v>211</v>
+      <c r="G114" s="13" t="inlineStr">
+        <is>
+          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+        </is>
       </c>
       <c r="H114" s="8" t="s">
         <v>205</v>
@@ -4360,8 +4401,8 @@
         <v>2</v>
       </c>
       <c r="J114">
-        <f t="shared" si="6"/>
-        <v>4.0252034654646121</v>
+        <f>5.059474185196228</f>
+        <v>5.059474185196228</v>
       </c>
       <c r="K114" s="6">
         <v>1.5</v>
@@ -4385,7 +4426,17 @@
         <v>2</v>
       </c>
       <c r="R114">
-        <f t="shared" si="7"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K114),2)
++POWER(LN(L114),2)
++POWER(LN(M114),2)
++POWER(LN(N114),2)
++POWER(LN(O114),2)
++POWER(LN(P114),2)
++POWER(LN(Q114),2)
+)
+)))</f>
         <v>0.58422518478336083</v>
       </c>
     </row>
@@ -4394,7 +4445,7 @@
         <v>19</v>
       </c>
       <c r="B115" s="14">
-        <v>7914.4736000000003</v>
+        <v>6319.509972236697</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>2</v>
@@ -4415,8 +4466,8 @@
         <v>2</v>
       </c>
       <c r="J115">
-        <f t="shared" si="6"/>
-        <v>8.9764484634704722</v>
+        <f>8.751396948096332</f>
+        <v>8.751396948096332</v>
       </c>
       <c r="K115" s="6">
         <v>1.5</v>
@@ -4440,7 +4491,17 @@
         <v>2</v>
       </c>
       <c r="R115">
-        <f t="shared" si="7"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K115),2)
++POWER(LN(L115),2)
++POWER(LN(M115),2)
++POWER(LN(N115),2)
++POWER(LN(O115),2)
++POWER(LN(P115),2)
++POWER(LN(Q115),2)
+)
+)))</f>
         <v>0.58422518478336083</v>
       </c>
     </row>
@@ -4537,8 +4598,10 @@
       <c r="A123" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B123" s="8" t="s">
-        <v>201</v>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED HYDROGEN PIPELINE GEOMETRY AND MATERIAL BOUNDARY, issue73,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly. Distribution selection is an explicit engineering adaptation,not an independently pressure-certified19bar pipeline:OD105mm,ID100mm=&gt;wall2.5mm,not copied4.5mm or27.09*(5/55). Steel density7850kg/m3 gives6319.509972236697kg/km; buy steel material AND equal pipe-drawing service,not two steel material inputs. Galvalume retainedmass=innerarea*pi*ID*length*65um*alloydensity; idealvolume-additive density=1/(.55/2700+.434/7140+.016/2330)=3685.2098164751933kg/m3. Transmission innerarea3660m2 fromsource gives876.7114153394484kg/km; distribution innerarea314.159m2 gives75.25328256144047kg/km. Thickness65um and idealalloydensity are explicitreferencechoices; actualmeasuredcoatingdensity/roughness/porosity need verification,test thickness30-100um. SourceGalvalume is reportedm2,notkg:original446.05kg cannot be transferred unchangedacrossdiameters. Both now buy issue72kgretainedalloy provider; its95%metalyield and unresolvedsodaash/processanomalies remainvisible. HDPEannulus outside25umFBE and0.5mmHDPE at950kg/m3 gives157.50767467854035kg/km; feedfullHDPEgranulateandmatchingextrusionservice,notextrusiononly. Transmission5599.17kgHDPE retainedassourced,not rederived underdistributiongeometry. NewHDPEprovider100%retentionreference,processscrap/yieldgapexplicit,test95-100%; no inventednegativeplasticcredit. Powdercoating native reference documents80um architecturalpowder,NOT source-specificFBE:purchase actualouterarea*selectedthickness/80um (25distribution,150transmission). This is an explicit thickness-proportional equivalent-area proxy including utilities; actualFBEresin/hardener,curingenergyperarea andservice-life gaps remain,not claimed industrialFBEreconstruction. Neither the addedHDPEfeed nor the coatservice includessteelmaterial. Freightretainseachoriginalimpliedmass-distance route for steel+Galvalume+HDPE,updatingtkmfornewretainedmass; excludesunknownpowder-retainedmass/sandfreight,asbefore. Distributiontrenchvolumes,sand,landuse/water andhelicoptersremainexistingperkmreferences ratherthan blindlyscaledbydiameteror100; trenchwidth andactualinstallationneedfieldvalidation. Service40years/0.22MtH2 and19bar distributionassumption retained,hydraulicsnotrecalculated; transmission40years/124.81Mtandcompressor125kmspacing unchanged. Treatment alreadyhas -1kmproduction andwrapper-1kmwasteinput:correctsigns preserved,not invertedorduplicated. Retainexisting50%landfill/treatment scenario as engineeringboundary,nowhalfretainedsteel+Galvalumemass toexistingdecommissionedpipeline treatment andhalfHDPE toexistingplastic treatment. Otherhalfmetal/polymerfate andpowdercoatingtreatment remainunresolved; no assumedprimary-secondaryshare,recoverycreditorclaimofcompleteEOLcoverage. Genericpipelinewastetreatment maycontainits ownlegacycomposition; not element-specificGalvalume recovery. Correctonlymisleadingdistributionmetadata; nativeprocesses/runtime/YAML unchanged. Geometry-derivedquantities:{'steel_kg_per_km': 6319.509972236697, 'Galvalume_kg_per_km': 75.25328256144047, 'HDPE_kg_per_km': 157.50767467854035}.</t>
+        </is>
       </c>
       <c r="K123" s="9"/>
       <c r="L123" s="9"/>
@@ -4685,7 +4748,7 @@
         <v>2</v>
       </c>
       <c r="J128">
-        <f t="shared" ref="J128:J131" si="8">LN(B128)</f>
+        <f>LN(B128)</f>
         <v>2.4849066497880004</v>
       </c>
       <c r="K128" s="6">
@@ -4710,7 +4773,7 @@
         <v>3</v>
       </c>
       <c r="R128">
-        <f t="shared" ref="R128:R131" si="9">LN(SQRT(EXP(
+        <f>LN(SQRT(EXP(
 SQRT(
 +POWER(LN(K128),2)
 +POWER(LN(L128),2)
@@ -4750,7 +4813,7 @@
         <v>2</v>
       </c>
       <c r="J129">
-        <f t="shared" si="8"/>
+        <f>LN(B129)</f>
         <v>5.2470240721604862</v>
       </c>
       <c r="K129" s="6">
@@ -4775,7 +4838,17 @@
         <v>3</v>
       </c>
       <c r="R129">
-        <f t="shared" si="9"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K129),2)
++POWER(LN(L129),2)
++POWER(LN(M129),2)
++POWER(LN(N129),2)
++POWER(LN(O129),2)
++POWER(LN(P129),2)
++POWER(LN(Q129),2)
+)
+)))</f>
         <v>0.79670949487272646</v>
       </c>
     </row>
@@ -4805,7 +4878,7 @@
         <v>2</v>
       </c>
       <c r="J130">
-        <f t="shared" si="8"/>
+        <f>LN(B130)</f>
         <v>10.034515814942532</v>
       </c>
       <c r="K130" s="6">
@@ -4830,7 +4903,17 @@
         <v>3</v>
       </c>
       <c r="R130">
-        <f t="shared" si="9"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K130),2)
++POWER(LN(L130),2)
++POWER(LN(M130),2)
++POWER(LN(N130),2)
++POWER(LN(O130),2)
++POWER(LN(P130),2)
++POWER(LN(Q130),2)
+)
+)))</f>
         <v>0.71779376269979156</v>
       </c>
     </row>
@@ -4839,7 +4922,7 @@
         <v>73</v>
       </c>
       <c r="B131" s="9">
-        <v>1201.7149000000002</v>
+        <v>935.5370155138878</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>74</v>
@@ -4860,8 +4943,8 @@
         <v>2</v>
       </c>
       <c r="J131">
-        <f t="shared" si="8"/>
-        <v>7.0915048989416594</v>
+        <f>6.841120712557115</f>
+        <v>6.841120712557115</v>
       </c>
       <c r="K131" s="6">
         <v>1.5</v>
@@ -4885,7 +4968,17 @@
         <v>3</v>
       </c>
       <c r="R131">
-        <f t="shared" si="9"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K131),2)
++POWER(LN(L131),2)
++POWER(LN(M131),2)
++POWER(LN(N131),2)
++POWER(LN(O131),2)
++POWER(LN(P131),2)
++POWER(LN(Q131),2)
+)
+)))</f>
         <v>0.79670949487272646</v>
       </c>
     </row>
@@ -4941,7 +5034,7 @@
         <v>3</v>
       </c>
       <c r="B136" s="8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K136" s="9"/>
       <c r="L136" s="9"/>
@@ -4982,8 +5075,10 @@
       <c r="A139" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B139" s="8" t="s">
-        <v>201</v>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED HYDROGEN PIPELINE GEOMETRY AND MATERIAL BOUNDARY, issue73,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly. Distribution selection is an explicit engineering adaptation,not an independently pressure-certified19bar pipeline:OD105mm,ID100mm=&gt;wall2.5mm,not copied4.5mm or27.09*(5/55). Steel density7850kg/m3 gives6319.509972236697kg/km; buy steel material AND equal pipe-drawing service,not two steel material inputs. Galvalume retainedmass=innerarea*pi*ID*length*65um*alloydensity; idealvolume-additive density=1/(.55/2700+.434/7140+.016/2330)=3685.2098164751933kg/m3. Transmission innerarea3660m2 fromsource gives876.7114153394484kg/km; distribution innerarea314.159m2 gives75.25328256144047kg/km. Thickness65um and idealalloydensity are explicitreferencechoices; actualmeasuredcoatingdensity/roughness/porosity need verification,test thickness30-100um. SourceGalvalume is reportedm2,notkg:original446.05kg cannot be transferred unchangedacrossdiameters. Both now buy issue72kgretainedalloy provider; its95%metalyield and unresolvedsodaash/processanomalies remainvisible. HDPEannulus outside25umFBE and0.5mmHDPE at950kg/m3 gives157.50767467854035kg/km; feedfullHDPEgranulateandmatchingextrusionservice,notextrusiononly. Transmission5599.17kgHDPE retainedassourced,not rederived underdistributiongeometry. NewHDPEprovider100%retentionreference,processscrap/yieldgapexplicit,test95-100%; no inventednegativeplasticcredit. Powdercoating native reference documents80um architecturalpowder,NOT source-specificFBE:purchase actualouterarea*selectedthickness/80um (25distribution,150transmission). This is an explicit thickness-proportional equivalent-area proxy including utilities; actualFBEresin/hardener,curingenergyperarea andservice-life gaps remain,not claimed industrialFBEreconstruction. Neither the addedHDPEfeed nor the coatservice includessteelmaterial. Freightretainseachoriginalimpliedmass-distance route for steel+Galvalume+HDPE,updatingtkmfornewretainedmass; excludesunknownpowder-retainedmass/sandfreight,asbefore. Distributiontrenchvolumes,sand,landuse/water andhelicoptersremainexistingperkmreferences ratherthan blindlyscaledbydiameteror100; trenchwidth andactualinstallationneedfieldvalidation. Service40years/0.22MtH2 and19bar distributionassumption retained,hydraulicsnotrecalculated; transmission40years/124.81Mtandcompressor125kmspacing unchanged. Treatment alreadyhas -1kmproduction andwrapper-1kmwasteinput:correctsigns preserved,not invertedorduplicated. Retainexisting50%landfill/treatment scenario as engineeringboundary,nowhalfretainedsteel+Galvalumemass toexistingdecommissionedpipeline treatment andhalfHDPE toexistingplastic treatment. Otherhalfmetal/polymerfate andpowdercoatingtreatment remainunresolved; no assumedprimary-secondaryshare,recoverycreditorclaimofcompleteEOLcoverage. Genericpipelinewastetreatment maycontainits ownlegacycomposition; not element-specificGalvalume recovery. Correctonlymisleadingdistributionmetadata; nativeprocesses/runtime/YAML unchanged. Geometry-derivedquantities:{'steel_kg_per_km': 6319.509972236697, 'Galvalume_kg_per_km': 75.25328256144047, 'HDPE_kg_per_km': 157.50767467854035}.</t>
+        </is>
       </c>
       <c r="K139" s="9"/>
       <c r="L139" s="9"/>
@@ -5110,7 +5205,7 @@
         <v>65</v>
       </c>
       <c r="B144" s="8">
-        <v>-3958.9524000000001</v>
+        <v>-3197.3816273990687</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>66</v>
@@ -5131,8 +5226,8 @@
         <v>2</v>
       </c>
       <c r="J144">
-        <f>LN(B144*-1)</f>
-        <v>8.2837347237956589</v>
+        <f>8.07008751240778</f>
+        <v>8.07008751240778</v>
       </c>
       <c r="K144" s="6">
         <v>1.5</v>
@@ -5156,7 +5251,7 @@
         <v>1.05</v>
       </c>
       <c r="R144">
-        <f t="shared" ref="R144:R145" si="10">LN(SQRT(EXP(
+        <f>LN(SQRT(EXP(
 SQRT(
 +POWER(LN(K144),2)
 +POWER(LN(L144),2)
@@ -5178,7 +5273,7 @@
         <v>216</v>
       </c>
       <c r="B145" s="8">
-        <v>-27.324000000000002</v>
+        <v>-78.75383733927018</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>217</v>
@@ -5199,8 +5294,8 @@
         <v>2</v>
       </c>
       <c r="J145">
-        <f>LN(B145*-1)</f>
-        <v>3.307765436869603</v>
+        <f>4.3663270046362825</f>
+        <v>4.3663270046362825</v>
       </c>
       <c r="K145" s="6">
         <v>1.5</v>
@@ -5224,7 +5319,17 @@
         <v>1.05</v>
       </c>
       <c r="R145">
-        <f t="shared" si="10"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K145),2)
++POWER(LN(L145),2)
++POWER(LN(M145),2)
++POWER(LN(N145),2)
++POWER(LN(O145),2)
++POWER(LN(P145),2)
++POWER(LN(Q145),2)
+)
+)))</f>
         <v>0.57758453844188851</v>
       </c>
       <c r="S145" s="8" t="b">
@@ -5323,7 +5428,9 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>APPROVED EXPLICIT GALVALUME METAL FEED, issue72,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook. Introducea clearlydefined1kgretainedGalvalume coatingreference with0.55kgAl,0.434kgZn,0.016kgSi. Itisnot1kgpureZn,nor1kgcoatedsteel,andsodaashcannotprovideZn. UsegenericwroughtAl,marketZn andmetallurgicalSisupply; forming/galvanicalloying1kWh/kg explicitengineeringassemblyallowance.95%metalretention reference,test90-100%;grossfeeds=retained/.95,pairedmixedmanufacturingwaste=(1/.95-1)kgminusdeclaredZnrelease2.94e-5kg. DetailedZn/Al/Si-specificlossfatesunresolved; donot countallscrapasrecoverablemetal. Copyotherexistingpublicbathchemical/utility/emissionprocess coefficients as a DOCUMENTEDPROXY,not verifiedmodernapplicationdata. Inparticularretain1kgsodaash/kgcoatingconservatively becausetheoriginalWulfS3explicitlysays1000kg/tonne; thereisnosourcedbasis to silentlyreplaceitbyZn ordeletea potentialbathchemical. Thisanomalouschemicalintensity remains a quantified sourcegap,not a closedindustrialrecipe. HeatCHPunit/source dust-factor anomalies arelikewiseunresolvedinexistingprocessreference; no fullprocesscertification. Thusnumericalmetalfeedisnowexplicitwhileuncertainnonmetalprocessburdensremainvisible. ExistingZn/othertraceemissionsretainedfromsource;subtractZnreleasefrommatchednetmetallosswasteforno doublemetal-lossaccount. Thisdoesnotbalanceunmeasuredtraceelementsinbathchemicals. No globalnativegalvanizingedit. Rewirebothpipelineconstructioncoatingpurchases tothis1kgfinishedcoatingprovider atunchanged446.05kg/km inthiscommit; issue73 separatelycorrects geometricdose andpolymer/lifecycleboundary. Originallegacycoatingprovider retainedforcompatibility andannotatedwithknownsourceproblem. ActualpipelineGalvalumegrade isdocumented55/43.4/1.6; layerthicknessandcoatedarea addressednext. Noassumedzerozincor unsupportedcredit.
+          <t>APPROVED HYDROGEN PIPELINE GEOMETRY AND MATERIAL BOUNDARY, issue73,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly. Distribution selection is an explicit engineering adaptation,not an independently pressure-certified19bar pipeline:OD105mm,ID100mm=&gt;wall2.5mm,not copied4.5mm or27.09*(5/55). Steel density7850kg/m3 gives6319.509972236697kg/km; buy steel material AND equal pipe-drawing service,not two steel material inputs. Galvalume retainedmass=innerarea*pi*ID*length*65um*alloydensity; idealvolume-additive density=1/(.55/2700+.434/7140+.016/2330)=3685.2098164751933kg/m3. Transmission innerarea3660m2 fromsource gives876.7114153394484kg/km; distribution innerarea314.159m2 gives75.25328256144047kg/km. Thickness65um and idealalloydensity are explicitreferencechoices; actualmeasuredcoatingdensity/roughness/porosity need verification,test thickness30-100um. SourceGalvalume is reportedm2,notkg:original446.05kg cannot be transferred unchangedacrossdiameters. Both now buy issue72kgretainedalloy provider; its95%metalyield and unresolvedsodaash/processanomalies remainvisible. HDPEannulus outside25umFBE and0.5mmHDPE at950kg/m3 gives157.50767467854035kg/km; feedfullHDPEgranulateandmatchingextrusionservice,notextrusiononly. Transmission5599.17kgHDPE retainedassourced,not rederived underdistributiongeometry. NewHDPEprovider100%retentionreference,processscrap/yieldgapexplicit,test95-100%; no inventednegativeplasticcredit. Powdercoating native reference documents80um architecturalpowder,NOT source-specificFBE:purchase actualouterarea*selectedthickness/80um (25distribution,150transmission). This is an explicit thickness-proportional equivalent-area proxy including utilities; actualFBEresin/hardener,curingenergyperarea andservice-life gaps remain,not claimed industrialFBEreconstruction. Neither the addedHDPEfeed nor the coatservice includessteelmaterial. Freightretainseachoriginalimpliedmass-distance route for steel+Galvalume+HDPE,updatingtkmfornewretainedmass; excludesunknownpowder-retainedmass/sandfreight,asbefore. Distributiontrenchvolumes,sand,landuse/water andhelicoptersremainexistingperkmreferences ratherthan blindlyscaledbydiameteror100; trenchwidth andactualinstallationneedfieldvalidation. Service40years/0.22MtH2 and19bar distributionassumption retained,hydraulicsnotrecalculated; transmission40years/124.81Mtandcompressor125kmspacing unchanged. Treatment alreadyhas -1kmproduction andwrapper-1kmwasteinput:correctsigns preserved,not invertedorduplicated. Retainexisting50%landfill/treatment scenario as engineeringboundary,nowhalfretainedsteel+Galvalumemass toexistingdecommissionedpipeline treatment andhalfHDPE toexistingplastic treatment. Otherhalfmetal/polymerfate andpowdercoatingtreatment remainunresolved; no assumedprimary-secondaryshare,recoverycreditorclaimofcompleteEOLcoverage. Genericpipelinewastetreatment maycontainits ownlegacycomposition; not element-specificGalvalume recovery. Correctonlymisleadingdistributionmetadata; nativeprocesses/runtime/YAML unchanged. Geometry-derivedquantities:{'steel_kg_per_km': 6319.509972236697, 'Galvalume_kg_per_km': 75.25328256144047, 'HDPE_kg_per_km': 157.50767467854035}.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED EXPLICIT GALVALUME METAL FEED, issue72,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook. Introducea clearlydefined1kgretainedGalvalume coatingreference with0.55kgAl,0.434kgZn,0.016kgSi. Itisnot1kgpureZn,nor1kgcoatedsteel,andsodaashcannotprovideZn. UsegenericwroughtAl,marketZn andmetallurgicalSisupply; forming/galvanicalloying1kWh/kg explicitengineeringassemblyallowance.95%metalretention reference,test90-100%;grossfeeds=retained/.95,pairedmixedmanufacturingwaste=(1/.95-1)kgminusdeclaredZnrelease2.94e-5kg. DetailedZn/Al/Si-specificlossfatesunresolved; donot countallscrapasrecoverablemetal. Copyotherexistingpublicbathchemical/utility/emissionprocess coefficients as a DOCUMENTEDPROXY,not verifiedmodernapplicationdata. Inparticularretain1kgsodaash/kgcoatingconservatively becausetheoriginalWulfS3explicitlysays1000kg/tonne; thereisnosourcedbasis to silentlyreplaceitbyZn ordeletea potentialbathchemical. Thisanomalouschemicalintensity remains a quantified sourcegap,not a closedindustrialrecipe. HeatCHPunit/source dust-factor anomalies arelikewiseunresolvedinexistingprocessreference; no fullprocesscertification. Thusnumericalmetalfeedisnowexplicitwhileuncertainnonmetalprocessburdensremainvisible. ExistingZn/othertraceemissionsretainedfromsource;subtractZnreleasefrommatchednetmetallosswasteforno doublemetal-lossaccount. Thisdoesnotbalanceunmeasuredtraceelementsinbathchemicals. No globalnativegalvanizingedit. Rewirebothpipelineconstructioncoatingpurchases tothis1kgfinishedcoatingprovider atunchanged446.05kg/km inthiscommit; issue73 separatelycorrects geometricdose andpolymer/lifecycleboundary. Originallegacycoatingprovider retainedforcompatibility andannotatedwithknownsourceproblem. ActualpipelineGalvalumegrade isdocumented55/43.4/1.6; layerthicknessandcoatedarea addressednext. Noassumedzerozincor unsupportedcredit.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 LCI of 1 km of transmission pipeline, source from C. Tsiklios, M. Hermesmann, T.E. Müller, Hydrogen transport in large-scale transmission pipeline networks: Thermodynamic and environmental assessment of repurposed and new pipeline configurations, Applied Energy, 2022, https://doi.org/10.1016/j.apenergy.2022.120097.
 Transmission pipeline
@@ -5484,7 +5591,7 @@
         <v>2</v>
       </c>
       <c r="J158">
-        <f t="shared" ref="J158:J164" si="11">LN(B158)</f>
+        <f>LN(B158)</f>
         <v>-1.6094379124341003</v>
       </c>
       <c r="K158" s="6">
@@ -5509,7 +5616,7 @@
         <v>3</v>
       </c>
       <c r="R158">
-        <f t="shared" ref="R158:R164" si="12">LN(SQRT(EXP(
+        <f>LN(SQRT(EXP(
 SQRT(
 +POWER(LN(K158),2)
 +POWER(LN(L158),2)
@@ -5549,7 +5656,7 @@
         <v>2</v>
       </c>
       <c r="J159">
-        <f t="shared" si="11"/>
+        <f>LN(B159)</f>
         <v>2.7725887222397811</v>
       </c>
       <c r="K159" s="6">
@@ -5574,7 +5681,17 @@
         <v>3</v>
       </c>
       <c r="R159">
-        <f t="shared" si="12"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K159),2)
++POWER(LN(L159),2)
++POWER(LN(M159),2)
++POWER(LN(N159),2)
++POWER(LN(O159),2)
++POWER(LN(P159),2)
++POWER(LN(Q159),2)
+)
+)))</f>
         <v>0.72314801614797197</v>
       </c>
     </row>
@@ -5604,7 +5721,7 @@
         <v>2</v>
       </c>
       <c r="J160">
-        <f t="shared" si="11"/>
+        <f>13.581618649458564</f>
         <v>13.581618649458564</v>
       </c>
       <c r="K160" s="6">
@@ -5629,7 +5746,17 @@
         <v>2</v>
       </c>
       <c r="R160">
-        <f t="shared" si="12"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K160),2)
++POWER(LN(L160),2)
++POWER(LN(M160),2)
++POWER(LN(N160),2)
++POWER(LN(O160),2)
++POWER(LN(P160),2)
++POWER(LN(Q160),2)
+)
+)))</f>
         <v>0.58422518478336083</v>
       </c>
     </row>
@@ -5638,7 +5765,7 @@
         <v>209</v>
       </c>
       <c r="B161" s="14">
-        <v>3830.23</v>
+        <v>7181.68125</v>
       </c>
       <c r="C161" s="8" t="s">
         <v>41</v>
@@ -5659,8 +5786,8 @@
         <v>2</v>
       </c>
       <c r="J161">
-        <f t="shared" si="11"/>
-        <v>8.2506801325909507</v>
+        <f>8.879288792013325</f>
+        <v>8.879288792013325</v>
       </c>
       <c r="K161" s="6">
         <v>1.5</v>
@@ -5684,7 +5811,17 @@
         <v>2</v>
       </c>
       <c r="R161">
-        <f t="shared" si="12"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K161),2)
++POWER(LN(L161),2)
++POWER(LN(M161),2)
++POWER(LN(N161),2)
++POWER(LN(O161),2)
++POWER(LN(P161),2)
++POWER(LN(Q161),2)
+)
+)))</f>
         <v>0.58422518478336083</v>
       </c>
     </row>
@@ -5695,7 +5832,7 @@
         </is>
       </c>
       <c r="B162" s="8">
-        <v>446.05</v>
+        <v>876.7114153394484</v>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
@@ -5720,8 +5857,8 @@
         <v>2</v>
       </c>
       <c r="J162">
-        <f t="shared" si="11"/>
-        <v>6.1004310533597925</v>
+        <f>6.776177879314433</f>
+        <v>6.776177879314433</v>
       </c>
       <c r="K162" s="6">
         <v>1.5</v>
@@ -5745,28 +5882,46 @@
         <v>2</v>
       </c>
       <c r="R162">
-        <f t="shared" si="12"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K162),2)
++POWER(LN(L162),2)
++POWER(LN(M162),2)
++POWER(LN(N162),2)
++POWER(LN(O162),2)
++POWER(LN(P162),2)
++POWER(LN(Q162),2)
+)
+)))</f>
         <v>0.58422518478336083</v>
       </c>
     </row>
     <row r="163" spans="1:20" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A163" s="13" t="s">
-        <v>211</v>
+      <c r="A163" s="13" t="inlineStr">
+        <is>
+          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+        </is>
       </c>
       <c r="B163" s="14">
         <v>5599.17</v>
       </c>
-      <c r="C163" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D163" s="8" t="s">
-        <v>21</v>
+      <c r="C163" s="8" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
       </c>
       <c r="F163" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G163" s="13" t="s">
-        <v>211</v>
+      <c r="G163" s="13" t="inlineStr">
+        <is>
+          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+        </is>
       </c>
       <c r="H163" s="8" t="s">
         <v>205</v>
@@ -5775,8 +5930,8 @@
         <v>2</v>
       </c>
       <c r="J163">
-        <f t="shared" si="11"/>
-        <v>8.6303736514527039</v>
+        <f>8.630373651452704</f>
+        <v>8.630373651452704</v>
       </c>
       <c r="K163" s="6">
         <v>1.5</v>
@@ -5800,7 +5955,17 @@
         <v>2</v>
       </c>
       <c r="R163">
-        <f t="shared" si="12"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K163),2)
++POWER(LN(L163),2)
++POWER(LN(M163),2)
++POWER(LN(N163),2)
++POWER(LN(O163),2)
++POWER(LN(P163),2)
++POWER(LN(Q163),2)
+)
+)))</f>
         <v>0.58422518478336083</v>
       </c>
     </row>
@@ -5830,7 +5995,7 @@
         <v>2</v>
       </c>
       <c r="J164">
-        <f t="shared" si="11"/>
+        <f>13.581618649458564</f>
         <v>13.581618649458564</v>
       </c>
       <c r="K164" s="6">
@@ -5855,7 +6020,17 @@
         <v>2</v>
       </c>
       <c r="R164">
-        <f t="shared" si="12"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K164),2)
++POWER(LN(L164),2)
++POWER(LN(M164),2)
++POWER(LN(N164),2)
++POWER(LN(O164),2)
++POWER(LN(P164),2)
++POWER(LN(Q164),2)
+)
+)))</f>
         <v>0.58422518478336083</v>
       </c>
     </row>
@@ -5952,8 +6127,23 @@
       <c r="A172" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B172" s="8" t="s">
-        <v>219</v>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED HYDROGEN PIPELINE GEOMETRY AND MATERIAL BOUNDARY, issue73,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly. Distribution selection is an explicit engineering adaptation,not an independently pressure-certified19bar pipeline:OD105mm,ID100mm=&gt;wall2.5mm,not copied4.5mm or27.09*(5/55). Steel density7850kg/m3 gives6319.509972236697kg/km; buy steel material AND equal pipe-drawing service,not two steel material inputs. Galvalume retainedmass=innerarea*pi*ID*length*65um*alloydensity; idealvolume-additive density=1/(.55/2700+.434/7140+.016/2330)=3685.2098164751933kg/m3. Transmission innerarea3660m2 fromsource gives876.7114153394484kg/km; distribution innerarea314.159m2 gives75.25328256144047kg/km. Thickness65um and idealalloydensity are explicitreferencechoices; actualmeasuredcoatingdensity/roughness/porosity need verification,test thickness30-100um. SourceGalvalume is reportedm2,notkg:original446.05kg cannot be transferred unchangedacrossdiameters. Both now buy issue72kgretainedalloy provider; its95%metalyield and unresolvedsodaash/processanomalies remainvisible. HDPEannulus outside25umFBE and0.5mmHDPE at950kg/m3 gives157.50767467854035kg/km; feedfullHDPEgranulateandmatchingextrusionservice,notextrusiononly. Transmission5599.17kgHDPE retainedassourced,not rederived underdistributiongeometry. NewHDPEprovider100%retentionreference,processscrap/yieldgapexplicit,test95-100%; no inventednegativeplasticcredit. Powdercoating native reference documents80um architecturalpowder,NOT source-specificFBE:purchase actualouterarea*selectedthickness/80um (25distribution,150transmission). This is an explicit thickness-proportional equivalent-area proxy including utilities; actualFBEresin/hardener,curingenergyperarea andservice-life gaps remain,not claimed industrialFBEreconstruction. Neither the addedHDPEfeed nor the coatservice includessteelmaterial. Freightretainseachoriginalimpliedmass-distance route for steel+Galvalume+HDPE,updatingtkmfornewretainedmass; excludesunknownpowder-retainedmass/sandfreight,asbefore. Distributiontrenchvolumes,sand,landuse/water andhelicoptersremainexistingperkmreferences ratherthan blindlyscaledbydiameteror100; trenchwidth andactualinstallationneedfieldvalidation. Service40years/0.22MtH2 and19bar distributionassumption retained,hydraulicsnotrecalculated; transmission40years/124.81Mtandcompressor125kmspacing unchanged. Treatment alreadyhas -1kmproduction andwrapper-1kmwasteinput:correctsigns preserved,not invertedorduplicated. Retainexisting50%landfill/treatment scenario as engineeringboundary,nowhalfretainedsteel+Galvalumemass toexistingdecommissionedpipeline treatment andhalfHDPE toexistingplastic treatment. Otherhalfmetal/polymerfate andpowdercoatingtreatment remainunresolved; no assumedprimary-secondaryshare,recoverycreditorclaimofcompleteEOLcoverage. Genericpipelinewastetreatment maycontainits ownlegacycomposition; not element-specificGalvalume recovery. Correctonlymisleadingdistributionmetadata; nativeprocesses/runtime/YAML unchanged. Geometry-derivedquantities:{'steel_kg_per_km': 6319.509972236697, 'Galvalume_kg_per_km': 75.25328256144047, 'HDPE_kg_per_km': 157.50767467854035}.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+LCI of 1 km of transmission pipeline, source from C. Tsiklios, M. Hermesmann, T.E. Müller, Hydrogen transport in large-scale transmission pipeline networks: Thermodynamic and environmental assessment of repurposed and new pipeline configurations, Applied Energy, 2022, https://doi.org/10.1016/j.apenergy.2022.120097.
+Transmission pipeline
+Lifetime [years]: 40
+Operating pressure range [bar]: 16-100, 80 as reference
+Annual operating hours [hours]: 8,000
+Hydrogen circulated per lifetime [Mt]: 124.81
+Mass flow [kg/s]: 108.34
+Outer diameter [m]: 1.22
+Inner coating layer [micro-m]: 65
+Steel layer [mm]: 27.09
+Epoxy resin layer [mm]: 0.15
+HDPE layer [mm]: 3</t>
+        </is>
       </c>
       <c r="K172" s="9"/>
       <c r="L172" s="9"/>
@@ -6100,7 +6290,7 @@
         <v>2</v>
       </c>
       <c r="J177">
-        <f t="shared" ref="J177:J180" si="13">LN(B177)</f>
+        <f>LN(B177)</f>
         <v>7.0900768357760917</v>
       </c>
       <c r="K177" s="6">
@@ -6125,7 +6315,7 @@
         <v>3</v>
       </c>
       <c r="R177">
-        <f t="shared" ref="R177:R180" si="14">LN(SQRT(EXP(
+        <f>LN(SQRT(EXP(
 SQRT(
 +POWER(LN(K177),2)
 +POWER(LN(L177),2)
@@ -6165,7 +6355,7 @@
         <v>2</v>
       </c>
       <c r="J178">
-        <f t="shared" si="13"/>
+        <f>LN(B178)</f>
         <v>9.8521942581485771</v>
       </c>
       <c r="K178" s="6">
@@ -6190,7 +6380,17 @@
         <v>3</v>
       </c>
       <c r="R178">
-        <f t="shared" si="14"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K178),2)
++POWER(LN(L178),2)
++POWER(LN(M178),2)
++POWER(LN(N178),2)
++POWER(LN(O178),2)
++POWER(LN(P178),2)
++POWER(LN(Q178),2)
+)
+)))</f>
         <v>0.79670949487272646</v>
       </c>
     </row>
@@ -6220,7 +6420,7 @@
         <v>2</v>
       </c>
       <c r="J179">
-        <f t="shared" si="13"/>
+        <f>LN(B179)</f>
         <v>14.639686000930624</v>
       </c>
       <c r="K179" s="6">
@@ -6245,7 +6445,17 @@
         <v>3</v>
       </c>
       <c r="R179">
-        <f t="shared" si="14"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K179),2)
++POWER(LN(L179),2)
++POWER(LN(M179),2)
++POWER(LN(N179),2)
++POWER(LN(O179),2)
++POWER(LN(P179),2)
++POWER(LN(Q179),2)
+)
+)))</f>
         <v>0.71779376269979156</v>
       </c>
     </row>
@@ -6254,7 +6464,7 @@
         <v>73</v>
       </c>
       <c r="B180" s="9">
-        <v>120171.49</v>
+        <v>120236.38492851063</v>
       </c>
       <c r="C180" s="8" t="s">
         <v>74</v>
@@ -6275,8 +6485,8 @@
         <v>2</v>
       </c>
       <c r="J180">
-        <f t="shared" si="13"/>
-        <v>11.696675084929751</v>
+        <f>11.697214958510067</f>
+        <v>11.697214958510067</v>
       </c>
       <c r="K180" s="6">
         <v>1.5</v>
@@ -6300,7 +6510,17 @@
         <v>3</v>
       </c>
       <c r="R180">
-        <f t="shared" si="14"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K180),2)
++POWER(LN(L180),2)
++POWER(LN(M180),2)
++POWER(LN(N180),2)
++POWER(LN(O180),2)
++POWER(LN(P180),2)
++POWER(LN(Q180),2)
+)
+)))</f>
         <v>0.79670949487272646</v>
       </c>
     </row>
@@ -6356,7 +6576,7 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K185" s="9"/>
       <c r="L185" s="9"/>
@@ -6397,8 +6617,23 @@
       <c r="A188" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B188" s="8" t="s">
-        <v>219</v>
+      <c r="B188" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED HYDROGEN PIPELINE GEOMETRY AND MATERIAL BOUNDARY, issue73,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly. Distribution selection is an explicit engineering adaptation,not an independently pressure-certified19bar pipeline:OD105mm,ID100mm=&gt;wall2.5mm,not copied4.5mm or27.09*(5/55). Steel density7850kg/m3 gives6319.509972236697kg/km; buy steel material AND equal pipe-drawing service,not two steel material inputs. Galvalume retainedmass=innerarea*pi*ID*length*65um*alloydensity; idealvolume-additive density=1/(.55/2700+.434/7140+.016/2330)=3685.2098164751933kg/m3. Transmission innerarea3660m2 fromsource gives876.7114153394484kg/km; distribution innerarea314.159m2 gives75.25328256144047kg/km. Thickness65um and idealalloydensity are explicitreferencechoices; actualmeasuredcoatingdensity/roughness/porosity need verification,test thickness30-100um. SourceGalvalume is reportedm2,notkg:original446.05kg cannot be transferred unchangedacrossdiameters. Both now buy issue72kgretainedalloy provider; its95%metalyield and unresolvedsodaash/processanomalies remainvisible. HDPEannulus outside25umFBE and0.5mmHDPE at950kg/m3 gives157.50767467854035kg/km; feedfullHDPEgranulateandmatchingextrusionservice,notextrusiononly. Transmission5599.17kgHDPE retainedassourced,not rederived underdistributiongeometry. NewHDPEprovider100%retentionreference,processscrap/yieldgapexplicit,test95-100%; no inventednegativeplasticcredit. Powdercoating native reference documents80um architecturalpowder,NOT source-specificFBE:purchase actualouterarea*selectedthickness/80um (25distribution,150transmission). This is an explicit thickness-proportional equivalent-area proxy including utilities; actualFBEresin/hardener,curingenergyperarea andservice-life gaps remain,not claimed industrialFBEreconstruction. Neither the addedHDPEfeed nor the coatservice includessteelmaterial. Freightretainseachoriginalimpliedmass-distance route for steel+Galvalume+HDPE,updatingtkmfornewretainedmass; excludesunknownpowder-retainedmass/sandfreight,asbefore. Distributiontrenchvolumes,sand,landuse/water andhelicoptersremainexistingperkmreferences ratherthan blindlyscaledbydiameteror100; trenchwidth andactualinstallationneedfieldvalidation. Service40years/0.22MtH2 and19bar distributionassumption retained,hydraulicsnotrecalculated; transmission40years/124.81Mtandcompressor125kmspacing unchanged. Treatment alreadyhas -1kmproduction andwrapper-1kmwasteinput:correctsigns preserved,not invertedorduplicated. Retainexisting50%landfill/treatment scenario as engineeringboundary,nowhalfretainedsteel+Galvalumemass toexistingdecommissionedpipeline treatment andhalfHDPE toexistingplastic treatment. Otherhalfmetal/polymerfate andpowdercoatingtreatment remainunresolved; no assumedprimary-secondaryshare,recoverycreditorclaimofcompleteEOLcoverage. Genericpipelinewastetreatment maycontainits ownlegacycomposition; not element-specificGalvalume recovery. Correctonlymisleadingdistributionmetadata; nativeprocesses/runtime/YAML unchanged. Geometry-derivedquantities:{'steel_kg_per_km': 6319.509972236697, 'Galvalume_kg_per_km': 75.25328256144047, 'HDPE_kg_per_km': 157.50767467854035}.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+LCI of 1 km of transmission pipeline, source from C. Tsiklios, M. Hermesmann, T.E. Müller, Hydrogen transport in large-scale transmission pipeline networks: Thermodynamic and environmental assessment of repurposed and new pipeline configurations, Applied Energy, 2022, https://doi.org/10.1016/j.apenergy.2022.120097.
+Transmission pipeline
+Lifetime [years]: 40
+Operating pressure range [bar]: 16-100, 80 as reference
+Annual operating hours [hours]: 8,000
+Hydrogen circulated per lifetime [Mt]: 124.81
+Mass flow [kg/s]: 108.34
+Outer diameter [m]: 1.22
+Inner coating layer [micro-m]: 65
+Steel layer [mm]: 27.09
+Epoxy resin layer [mm]: 0.15
+HDPE layer [mm]: 3</t>
+        </is>
       </c>
       <c r="K188" s="9"/>
       <c r="L188" s="9"/>
@@ -6525,7 +6760,7 @@
         <v>65</v>
       </c>
       <c r="B193" s="8">
-        <v>-395895.24</v>
+        <v>-396162.03570766974</v>
       </c>
       <c r="C193" s="8" t="s">
         <v>66</v>
@@ -6546,8 +6781,8 @@
         <v>2</v>
       </c>
       <c r="J193">
-        <f>LN(B193*-1)</f>
-        <v>12.888904909783751</v>
+        <f>12.889578587624843</f>
+        <v>12.889578587624843</v>
       </c>
       <c r="K193" s="6">
         <v>1.5</v>
@@ -6571,7 +6806,7 @@
         <v>1.05</v>
       </c>
       <c r="R193">
-        <f t="shared" ref="R193:R194" si="15">LN(SQRT(EXP(
+        <f>LN(SQRT(EXP(
 SQRT(
 +POWER(LN(K193),2)
 +POWER(LN(L193),2)
@@ -6593,7 +6828,7 @@
         <v>216</v>
       </c>
       <c r="B194" s="8">
-        <v>-2732.4</v>
+        <v>-2799.585</v>
       </c>
       <c r="C194" s="8" t="s">
         <v>217</v>
@@ -6614,8 +6849,8 @@
         <v>2</v>
       </c>
       <c r="J194">
-        <f>LN(B194*-1)</f>
-        <v>7.9129356228576944</v>
+        <f>7.9372264708927585</f>
+        <v>7.9372264708927585</v>
       </c>
       <c r="K194" s="6">
         <v>1.5</v>
@@ -6639,7 +6874,17 @@
         <v>1.05</v>
       </c>
       <c r="R194">
-        <f t="shared" si="15"/>
+        <f>LN(SQRT(EXP(
+SQRT(
++POWER(LN(K194),2)
++POWER(LN(L194),2)
++POWER(LN(M194),2)
++POWER(LN(N194),2)
++POWER(LN(O194),2)
++POWER(LN(P194),2)
++POWER(LN(Q194),2)
+)
+)))</f>
         <v>0.57758453844188851</v>
       </c>
       <c r="S194" s="8" t="b">
@@ -13219,6 +13464,247 @@
         </is>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B445">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>APPROVED HYDROGEN PIPELINE GEOMETRY AND MATERIAL BOUNDARY, issue73,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly. Distribution selection is an explicit engineering adaptation,not an independently pressure-certified19bar pipeline:OD105mm,ID100mm=&gt;wall2.5mm,not copied4.5mm or27.09*(5/55). Steel density7850kg/m3 gives6319.509972236697kg/km; buy steel material AND equal pipe-drawing service,not two steel material inputs. Galvalume retainedmass=innerarea*pi*ID*length*65um*alloydensity; idealvolume-additive density=1/(.55/2700+.434/7140+.016/2330)=3685.2098164751933kg/m3. Transmission innerarea3660m2 fromsource gives876.7114153394484kg/km; distribution innerarea314.159m2 gives75.25328256144047kg/km. Thickness65um and idealalloydensity are explicitreferencechoices; actualmeasuredcoatingdensity/roughness/porosity need verification,test thickness30-100um. SourceGalvalume is reportedm2,notkg:original446.05kg cannot be transferred unchangedacrossdiameters. Both now buy issue72kgretainedalloy provider; its95%metalyield and unresolvedsodaash/processanomalies remainvisible. HDPEannulus outside25umFBE and0.5mmHDPE at950kg/m3 gives157.50767467854035kg/km; feedfullHDPEgranulateandmatchingextrusionservice,notextrusiononly. Transmission5599.17kgHDPE retainedassourced,not rederived underdistributiongeometry. NewHDPEprovider100%retentionreference,processscrap/yieldgapexplicit,test95-100%; no inventednegativeplasticcredit. Powdercoating native reference documents80um architecturalpowder,NOT source-specificFBE:purchase actualouterarea*selectedthickness/80um (25distribution,150transmission). This is an explicit thickness-proportional equivalent-area proxy including utilities; actualFBEresin/hardener,curingenergyperarea andservice-life gaps remain,not claimed industrialFBEreconstruction. Neither the addedHDPEfeed nor the coatservice includessteelmaterial. Freightretainseachoriginalimpliedmass-distance route for steel+Galvalume+HDPE,updatingtkmfornewretainedmass; excludesunknownpowder-retainedmass/sandfreight,asbefore. Distributiontrenchvolumes,sand,landuse/water andhelicoptersremainexistingperkmreferences ratherthan blindlyscaledbydiameteror100; trenchwidth andactualinstallationneedfieldvalidation. Service40years/0.22MtH2 and19bar distributionassumption retained,hydraulicsnotrecalculated; transmission40years/124.81Mtandcompressor125kmspacing unchanged. Treatment alreadyhas -1kmproduction andwrapper-1kmwasteinput:correctsigns preserved,not invertedorduplicated. Retainexisting50%landfill/treatment scenario as engineeringboundary,nowhalfretainedsteel+Galvalumemass toexistingdecommissionedpipeline treatment andhalfHDPE toexistingplastic treatment. Otherhalfmetal/polymerfate andpowdercoatingtreatment remainunresolved; no assumedprimary-secondaryshare,recoverycreditorclaimofcompleteEOLcoverage. Genericpipelinewastetreatment maycontainits ownlegacycomposition; not element-specificGalvalume recovery. Correctonlymisleadingdistributionmetadata; nativeprocesses/runtime/YAML unchanged. Geometry-derivedquantities:{'steel_kg_per_km': 6319.509972236697, 'Galvalume_kg_per_km': 75.25328256144047, 'HDPE_kg_per_km': 157.50767467854035}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+        </is>
+      </c>
+      <c r="B452">
+        <v>1</v>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B453">
+        <v>1</v>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>extrusion, plastic film</t>
+        </is>
+      </c>
+      <c r="B454">
+        <v>1</v>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>extrusion, plastic film</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>extrusion, plastic film</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I365" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
@@ -1677,7 +1677,7 @@
     <row r="26" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>hydrogen storage tank system, station125kg H2 capacity, engineering reference</t>
+          <t xml:space="preserve">hydrogen storage tank system production, refuelling station, 125 kg hydrogen</t>
         </is>
       </c>
       <c r="B26">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>hydrogen storage tank system, station125kg H2 capacity, engineering reference</t>
+          <t xml:space="preserve">hydrogen storage tank system, refuelling station, 125 kg hydrogen</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
     <row r="113" spans="1:20" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+          <t xml:space="preserve">aluminium-zinc coating alloy production, for galvanizing</t>
         </is>
       </c>
       <c r="B113" s="8">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+          <t xml:space="preserve">aluminium-zinc coating alloy, for galvanizing</t>
         </is>
       </c>
       <c r="H113" s="8" t="s">
@@ -4370,7 +4370,7 @@
     <row r="114" spans="1:20" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+          <t xml:space="preserve">polyethylene coating production, high density, for pipelines</t>
         </is>
       </c>
       <c r="B114" s="14">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="G114" s="13" t="inlineStr">
         <is>
-          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+          <t xml:space="preserve">polyethylene coating, high density, for pipelines</t>
         </is>
       </c>
       <c r="H114" s="8" t="s">
@@ -5828,7 +5828,7 @@
     <row r="162" spans="1:20" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+          <t xml:space="preserve">aluminium-zinc coating alloy production, for galvanizing</t>
         </is>
       </c>
       <c r="B162" s="8">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+          <t xml:space="preserve">aluminium-zinc coating alloy, for galvanizing</t>
         </is>
       </c>
       <c r="H162" s="8" t="s">
@@ -5899,7 +5899,7 @@
     <row r="163" spans="1:20" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A163" s="13" t="inlineStr">
         <is>
-          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+          <t xml:space="preserve">polyethylene coating production, high density, for pipelines</t>
         </is>
       </c>
       <c r="B163" s="14">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="G163" s="13" t="inlineStr">
         <is>
-          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+          <t xml:space="preserve">polyethylene coating, high density, for pipelines</t>
         </is>
       </c>
       <c r="H163" s="8" t="s">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>hydrogen storage tank system, station125kg H2 capacity, engineering reference</t>
+          <t xml:space="preserve">hydrogen storage tank system production, refuelling station, 125 kg hydrogen</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>hydrogen storage tank system, station125kg H2 capacity, engineering reference</t>
+          <t xml:space="preserve">hydrogen storage tank system, refuelling station, 125 kg hydrogen</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,8 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>APPROVED HYDROGEN-STATION TANK CAPACITY/LIFE UNITS, issue71,2026-10-18. Wulf2018 publicSI DOI10.1016/j.jclepro.2018.07.180 TablesS6(per10kgH2storage) andS8(125kgH2storageforstation),plus workbook40yearstation/20yeartanklife assumptions. TheSI explicitlylists125kg for LOHC,pipelineandhighpressuretruckstation supplypaths. Originaltankkgoutput is kgH2STORAGECAPACITY,notkgdryvessel; sourceS6materials per10kgH2are6Al+9stainless+71.4carbonfiber+30.6epoxy+9lowalloysteel=126kgdry=&gt;12.6kgdry/kgH2capacity. Do not normalize126kgmaterial to10kgdrytank. Stationinstalledcapacity125kgH2 fromS8,20yearvessellife and40yearstationlife implytwo manufacturedsets inone40yearstationinventory,not two125kgvesselsinstalledandthenanotherreplacementfactor. Newunitprovider is one125kgH2capacity installedtankreference containing1575kgdrymaterial,includingits existingtankBoPproportions; sourcepressure,individualcylindercount andcertification unspecified,not labelled700barorbusType4without evidence. Stationbuystwounits total250kgH2capacity manufacture/3150kgdry overlife,exactlypreservingoriginalmaterial,processenergyandformingvectors afterissue70. No hiddennewrecyclingcredit,treatmentorsecondlifetime divisor; originalstationgenericEOLgap remains. Theoriginalkgprovider remainsavailableaslegacycapacityreference withclarifiedcomment,soexternalconsumers donot silently changefunctionalunit. Newexplicitunitprovider is activeforstationonly. Cylinderpressure/reserve/actualhydrogenusablefraction anddemandutilization arestillengineeringgaps. Existing850kg/daynameplate,70%utilization,595kg/dayhydrogen throughput and40yearserviceallocation are unchanged; no operationalcompression/precooling change. Neither3160kgwetmassnorstoredhydrogenfeed ismanufacturedmetal.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: hydrogen storage tank system, station125kg H2 capacity, engineering reference. Former reference product: hydrogen storage tank system, station125kg H2 capacity, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED HYDROGEN-STATION TANK CAPACITY/LIFE UNITS, issue71,2026-10-18. Wulf2018 publicSI DOI10.1016/j.jclepro.2018.07.180 TablesS6(per10kgH2storage) andS8(125kgH2storageforstation),plus workbook40yearstation/20yeartanklife assumptions. TheSI explicitlylists125kg for LOHC,pipelineandhighpressuretruckstation supplypaths. Originaltankkgoutput is kgH2STORAGECAPACITY,notkgdryvessel; sourceS6materials per10kgH2are6Al+9stainless+71.4carbonfiber+30.6epoxy+9lowalloysteel=126kgdry=&gt;12.6kgdry/kgH2capacity. Do not normalize126kgmaterial to10kgdrytank. Stationinstalledcapacity125kgH2 fromS8,20yearvessellife and40yearstationlife implytwo manufacturedsets inone40yearstationinventory,not two125kgvesselsinstalledandthenanotherreplacementfactor. Newunitprovider is one125kgH2capacity installedtankreference containing1575kgdrymaterial,includingits existingtankBoPproportions; sourcepressure,individualcylindercount andcertification unspecified,not labelled700barorbusType4without evidence. Stationbuystwounits total250kgH2capacity manufacture/3150kgdry overlife,exactlypreservingoriginalmaterial,processenergyandformingvectors afterissue70. No hiddennewrecyclingcredit,treatmentorsecondlifetime divisor; originalstationgenericEOLgap remains. Theoriginalkgprovider remainsavailableaslegacycapacityreference withclarifiedcomment,soexternalconsumers donot silently changefunctionalunit. Newexplicitunitprovider is activeforstationonly. Cylinderpressure/reserve/actualhydrogenusablefraction anddemandutilization arestillengineeringgaps. Existing850kg/daynameplate,70%utilization,595kg/dayhydrogen throughput and40yearserviceallocation are unchanged; no operationalcompression/precooling change. Neither3160kgwetmassnorstoredhydrogenfeed ismanufacturedmetal.</t>
         </is>
       </c>
     </row>
@@ -11551,7 +11552,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>hydrogen storage tank system, station125kg H2 capacity, engineering reference</t>
+          <t xml:space="preserve">hydrogen storage tank system production, refuelling station, 125 kg hydrogen</t>
         </is>
       </c>
       <c r="B376">
@@ -11574,12 +11575,12 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>hydrogen storage tank system, station125kg H2 capacity, engineering reference</t>
+          <t xml:space="preserve">hydrogen storage tank system, refuelling station, 125 kg hydrogen</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>hydrogen storage tank system, station125kg H2 capacity, engineering reference</t>
+          <t xml:space="preserve">hydrogen storage tank system, refuelling station, 125 kg hydrogen</t>
         </is>
       </c>
     </row>
@@ -11906,7 +11907,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+          <t xml:space="preserve">aluminium-zinc coating alloy production, for galvanizing</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11941,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+          <t xml:space="preserve">aluminium-zinc coating alloy, for galvanizing</t>
         </is>
       </c>
     </row>
@@ -11976,7 +11977,8 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>APPROVED EXPLICIT GALVALUME METAL FEED, issue72,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook. Introducea clearlydefined1kgretainedGalvalume coatingreference with0.55kgAl,0.434kgZn,0.016kgSi. Itisnot1kgpureZn,nor1kgcoatedsteel,andsodaashcannotprovideZn. UsegenericwroughtAl,marketZn andmetallurgicalSisupply; forming/galvanicalloying1kWh/kg explicitengineeringassemblyallowance.95%metalretention reference,test90-100%;grossfeeds=retained/.95,pairedmixedmanufacturingwaste=(1/.95-1)kgminusdeclaredZnrelease2.94e-5kg. DetailedZn/Al/Si-specificlossfatesunresolved; donot countallscrapasrecoverablemetal. Copyotherexistingpublicbathchemical/utility/emissionprocess coefficients as a DOCUMENTEDPROXY,not verifiedmodernapplicationdata. Inparticularretain1kgsodaash/kgcoatingconservatively becausetheoriginalWulfS3explicitlysays1000kg/tonne; thereisnosourcedbasis to silentlyreplaceitbyZn ordeletea potentialbathchemical. Thisanomalouschemicalintensity remains a quantified sourcegap,not a closedindustrialrecipe. HeatCHPunit/source dust-factor anomalies arelikewiseunresolvedinexistingprocessreference; no fullprocesscertification. Thusnumericalmetalfeedisnowexplicitwhileuncertainnonmetalprocessburdensremainvisible. ExistingZn/othertraceemissionsretainedfromsource;subtractZnreleasefrommatchednetmetallosswasteforno doublemetal-lossaccount. Thisdoesnotbalanceunmeasuredtraceelementsinbathchemicals. No globalnativegalvanizingedit. Rewirebothpipelineconstructioncoatingpurchases tothis1kgfinishedcoatingprovider atunchanged446.05kg/km inthiscommit; issue73 separatelycorrects geometricdose andpolymer/lifecycleboundary. Originallegacycoatingprovider retainedforcompatibility andannotatedwithknownsourceproblem. ActualpipelineGalvalumegrade isdocumented55/43.4/1.6; layerthicknessandcoatedarea addressednext. Noassumedzerozincor unsupportedcredit.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: Galvalume coating, retained alloy mass, engineering reference. Former reference product: Galvalume coating, retained alloy mass, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED EXPLICIT GALVALUME METAL FEED, issue72,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook. Introducea clearlydefined1kgretainedGalvalume coatingreference with0.55kgAl,0.434kgZn,0.016kgSi. Itisnot1kgpureZn,nor1kgcoatedsteel,andsodaashcannotprovideZn. UsegenericwroughtAl,marketZn andmetallurgicalSisupply; forming/galvanicalloying1kWh/kg explicitengineeringassemblyallowance.95%metalretention reference,test90-100%;grossfeeds=retained/.95,pairedmixedmanufacturingwaste=(1/.95-1)kgminusdeclaredZnrelease2.94e-5kg. DetailedZn/Al/Si-specificlossfatesunresolved; donot countallscrapasrecoverablemetal. Copyotherexistingpublicbathchemical/utility/emissionprocess coefficients as a DOCUMENTEDPROXY,not verifiedmodernapplicationdata. Inparticularretain1kgsodaash/kgcoatingconservatively becausetheoriginalWulfS3explicitlysays1000kg/tonne; thereisnosourcedbasis to silentlyreplaceitbyZn ordeletea potentialbathchemical. Thisanomalouschemicalintensity remains a quantified sourcegap,not a closedindustrialrecipe. HeatCHPunit/source dust-factor anomalies arelikewiseunresolvedinexistingprocessreference; no fullprocesscertification. Thusnumericalmetalfeedisnowexplicitwhileuncertainnonmetalprocessburdensremainvisible. ExistingZn/othertraceemissionsretainedfromsource;subtractZnreleasefrommatchednetmetallosswasteforno doublemetal-lossaccount. Thisdoesnotbalanceunmeasuredtraceelementsinbathchemicals. No globalnativegalvanizingedit. Rewirebothpipelineconstructioncoatingpurchases tothis1kgfinishedcoatingprovider atunchanged446.05kg/km inthiscommit; issue73 separatelycorrects geometricdose andpolymer/lifecycleboundary. Originallegacycoatingprovider retainedforcompatibility andannotatedwithknownsourceproblem. ActualpipelineGalvalumegrade isdocumented55/43.4/1.6; layerthicknessandcoatedarea addressednext. Noassumedzerozincor unsupportedcredit.</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12039,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+          <t xml:space="preserve">aluminium-zinc coating alloy production, for galvanizing</t>
         </is>
       </c>
       <c r="B397">
@@ -12060,12 +12062,12 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+          <t xml:space="preserve">aluminium-zinc coating alloy, for galvanizing</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>Galvalume coating, retained alloy mass, engineering reference</t>
+          <t xml:space="preserve">aluminium-zinc coating alloy, for galvanizing</t>
         </is>
       </c>
     </row>
@@ -13472,7 +13474,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+          <t xml:space="preserve">polyethylene coating production, high density, for pipelines</t>
         </is>
       </c>
     </row>
@@ -13506,7 +13508,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+          <t xml:space="preserve">polyethylene coating, high density, for pipelines</t>
         </is>
       </c>
     </row>
@@ -13542,7 +13544,8 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>APPROVED HYDROGEN PIPELINE GEOMETRY AND MATERIAL BOUNDARY, issue73,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly. Distribution selection is an explicit engineering adaptation,not an independently pressure-certified19bar pipeline:OD105mm,ID100mm=&gt;wall2.5mm,not copied4.5mm or27.09*(5/55). Steel density7850kg/m3 gives6319.509972236697kg/km; buy steel material AND equal pipe-drawing service,not two steel material inputs. Galvalume retainedmass=innerarea*pi*ID*length*65um*alloydensity; idealvolume-additive density=1/(.55/2700+.434/7140+.016/2330)=3685.2098164751933kg/m3. Transmission innerarea3660m2 fromsource gives876.7114153394484kg/km; distribution innerarea314.159m2 gives75.25328256144047kg/km. Thickness65um and idealalloydensity are explicitreferencechoices; actualmeasuredcoatingdensity/roughness/porosity need verification,test thickness30-100um. SourceGalvalume is reportedm2,notkg:original446.05kg cannot be transferred unchangedacrossdiameters. Both now buy issue72kgretainedalloy provider; its95%metalyield and unresolvedsodaash/processanomalies remainvisible. HDPEannulus outside25umFBE and0.5mmHDPE at950kg/m3 gives157.50767467854035kg/km; feedfullHDPEgranulateandmatchingextrusionservice,notextrusiononly. Transmission5599.17kgHDPE retainedassourced,not rederived underdistributiongeometry. NewHDPEprovider100%retentionreference,processscrap/yieldgapexplicit,test95-100%; no inventednegativeplasticcredit. Powdercoating native reference documents80um architecturalpowder,NOT source-specificFBE:purchase actualouterarea*selectedthickness/80um (25distribution,150transmission). This is an explicit thickness-proportional equivalent-area proxy including utilities; actualFBEresin/hardener,curingenergyperarea andservice-life gaps remain,not claimed industrialFBEreconstruction. Neither the addedHDPEfeed nor the coatservice includessteelmaterial. Freightretainseachoriginalimpliedmass-distance route for steel+Galvalume+HDPE,updatingtkmfornewretainedmass; excludesunknownpowder-retainedmass/sandfreight,asbefore. Distributiontrenchvolumes,sand,landuse/water andhelicoptersremainexistingperkmreferences ratherthan blindlyscaledbydiameteror100; trenchwidth andactualinstallationneedfieldvalidation. Service40years/0.22MtH2 and19bar distributionassumption retained,hydraulicsnotrecalculated; transmission40years/124.81Mtandcompressor125kmspacing unchanged. Treatment alreadyhas -1kmproduction andwrapper-1kmwasteinput:correctsigns preserved,not invertedorduplicated. Retainexisting50%landfill/treatment scenario as engineeringboundary,nowhalfretainedsteel+Galvalumemass toexistingdecommissionedpipeline treatment andhalfHDPE toexistingplastic treatment. Otherhalfmetal/polymerfate andpowdercoatingtreatment remainunresolved; no assumedprimary-secondaryshare,recoverycreditorclaimofcompleteEOLcoverage. Genericpipelinewastetreatment maycontainits ownlegacycomposition; not element-specificGalvalume recovery. Correctonlymisleadingdistributionmetadata; nativeprocesses/runtime/YAML unchanged. Geometry-derivedquantities:{'steel_kg_per_km': 6319.509972236697, 'Galvalume_kg_per_km': 75.25328256144047, 'HDPE_kg_per_km': 157.50767467854035}.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: HDPE pipeline coat, material and extrusion, engineering reference. Former reference product: HDPE pipeline coat, material and extrusion, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED HYDROGEN PIPELINE GEOMETRY AND MATERIAL BOUNDARY, issue73,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly. Distribution selection is an explicit engineering adaptation,not an independently pressure-certified19bar pipeline:OD105mm,ID100mm=&gt;wall2.5mm,not copied4.5mm or27.09*(5/55). Steel density7850kg/m3 gives6319.509972236697kg/km; buy steel material AND equal pipe-drawing service,not two steel material inputs. Galvalume retainedmass=innerarea*pi*ID*length*65um*alloydensity; idealvolume-additive density=1/(.55/2700+.434/7140+.016/2330)=3685.2098164751933kg/m3. Transmission innerarea3660m2 fromsource gives876.7114153394484kg/km; distribution innerarea314.159m2 gives75.25328256144047kg/km. Thickness65um and idealalloydensity are explicitreferencechoices; actualmeasuredcoatingdensity/roughness/porosity need verification,test thickness30-100um. SourceGalvalume is reportedm2,notkg:original446.05kg cannot be transferred unchangedacrossdiameters. Both now buy issue72kgretainedalloy provider; its95%metalyield and unresolvedsodaash/processanomalies remainvisible. HDPEannulus outside25umFBE and0.5mmHDPE at950kg/m3 gives157.50767467854035kg/km; feedfullHDPEgranulateandmatchingextrusionservice,notextrusiononly. Transmission5599.17kgHDPE retainedassourced,not rederived underdistributiongeometry. NewHDPEprovider100%retentionreference,processscrap/yieldgapexplicit,test95-100%; no inventednegativeplasticcredit. Powdercoating native reference documents80um architecturalpowder,NOT source-specificFBE:purchase actualouterarea*selectedthickness/80um (25distribution,150transmission). This is an explicit thickness-proportional equivalent-area proxy including utilities; actualFBEresin/hardener,curingenergyperarea andservice-life gaps remain,not claimed industrialFBEreconstruction. Neither the addedHDPEfeed nor the coatservice includessteelmaterial. Freightretainseachoriginalimpliedmass-distance route for steel+Galvalume+HDPE,updatingtkmfornewretainedmass; excludesunknownpowder-retainedmass/sandfreight,asbefore. Distributiontrenchvolumes,sand,landuse/water andhelicoptersremainexistingperkmreferences ratherthan blindlyscaledbydiameteror100; trenchwidth andactualinstallationneedfieldvalidation. Service40years/0.22MtH2 and19bar distributionassumption retained,hydraulicsnotrecalculated; transmission40years/124.81Mtandcompressor125kmspacing unchanged. Treatment alreadyhas -1kmproduction andwrapper-1kmwasteinput:correctsigns preserved,not invertedorduplicated. Retainexisting50%landfill/treatment scenario as engineeringboundary,nowhalfretainedsteel+Galvalumemass toexistingdecommissionedpipeline treatment andhalfHDPE toexistingplastic treatment. Otherhalfmetal/polymerfate andpowdercoatingtreatment remainunresolved; no assumedprimary-secondaryshare,recoverycreditorclaimofcompleteEOLcoverage. Genericpipelinewastetreatment maycontainits ownlegacycomposition; not element-specificGalvalume recovery. Correctonlymisleadingdistributionmetadata; nativeprocesses/runtime/YAML unchanged. Geometry-derivedquantities:{'steel_kg_per_km': 6319.509972236697, 'Galvalume_kg_per_km': 75.25328256144047, 'HDPE_kg_per_km': 157.50767467854035}.</t>
         </is>
       </c>
     </row>
@@ -13603,7 +13606,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+          <t xml:space="preserve">polyethylene coating production, high density, for pipelines</t>
         </is>
       </c>
       <c r="B452">
@@ -13626,12 +13629,12 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+          <t xml:space="preserve">polyethylene coating, high density, for pipelines</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>HDPE pipeline coat, material and extrusion, engineering reference</t>
+          <t xml:space="preserve">polyethylene coating, high density, for pipelines</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
@@ -6983,7 +6983,9 @@
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>APPROVED EXPLICIT GALVALUME METAL FEED, issue72,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook. Introducea clearlydefined1kgretainedGalvalume coatingreference with0.55kgAl,0.434kgZn,0.016kgSi. Itisnot1kgpureZn,nor1kgcoatedsteel,andsodaashcannotprovideZn. UsegenericwroughtAl,marketZn andmetallurgicalSisupply; forming/galvanicalloying1kWh/kg explicitengineeringassemblyallowance.95%metalretention reference,test90-100%;grossfeeds=retained/.95,pairedmixedmanufacturingwaste=(1/.95-1)kgminusdeclaredZnrelease2.94e-5kg. DetailedZn/Al/Si-specificlossfatesunresolved; donot countallscrapasrecoverablemetal. Copyotherexistingpublicbathchemical/utility/emissionprocess coefficients as a DOCUMENTEDPROXY,not verifiedmodernapplicationdata. Inparticularretain1kgsodaash/kgcoatingconservatively becausetheoriginalWulfS3explicitlysays1000kg/tonne; thereisnosourcedbasis to silentlyreplaceitbyZn ordeletea potentialbathchemical. Thisanomalouschemicalintensity remains a quantified sourcegap,not a closedindustrialrecipe. HeatCHPunit/source dust-factor anomalies arelikewiseunresolvedinexistingprocessreference; no fullprocesscertification. Thusnumericalmetalfeedisnowexplicitwhileuncertainnonmetalprocessburdensremainvisible. ExistingZn/othertraceemissionsretainedfromsource;subtractZnreleasefrommatchednetmetallosswasteforno doublemetal-lossaccount. Thisdoesnotbalanceunmeasuredtraceelementsinbathchemicals. No globalnativegalvanizingedit. Rewirebothpipelineconstructioncoatingpurchases tothis1kgfinishedcoatingprovider atunchanged446.05kg/km inthiscommit; issue73 separatelycorrects geometricdose andpolymer/lifecycleboundary. Originallegacycoatingprovider retainedforcompatibility andannotatedwithknownsourceproblem. ActualpipelineGalvalumegrade isdocumented55/43.4/1.6; layerthicknessandcoatedarea addressednext. Noassumedzerozincor unsupportedcredit.
+          <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source specifies14.7kg dust landfill treatment per1000kg coating, so the correct purchase is-0.0147kg/kg,not-0.000014kg/kg (1050times smaller than the source). Keep the existing native EAF dust disposal market: its production is-1kg and the negative purchase activates positive treatment. No new recovery credit or supplier-route substitution is introduced. The source-treatment dust assay is unreported; its ownership versus the separate nominal95%alloy-yield reject budget remains unqualified. A corrected transcription does not establish element closure between mixed process residues and separately modelled alloy loss. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED EXPLICIT GALVALUME METAL FEED, issue72,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook. Introducea clearlydefined1kgretainedGalvalume coatingreference with0.55kgAl,0.434kgZn,0.016kgSi. Itisnot1kgpureZn,nor1kgcoatedsteel,andsodaashcannotprovideZn. UsegenericwroughtAl,marketZn andmetallurgicalSisupply; forming/galvanicalloying1kWh/kg explicitengineeringassemblyallowance.95%metalretention reference,test90-100%;grossfeeds=retained/.95,pairedmixedmanufacturingwaste=(1/.95-1)kgminusdeclaredZnrelease2.94e-5kg. DetailedZn/Al/Si-specificlossfatesunresolved; donot countallscrapasrecoverablemetal. Copyotherexistingpublicbathchemical/utility/emissionprocess coefficients as a DOCUMENTEDPROXY,not verifiedmodernapplicationdata. Inparticularretain1kgsodaash/kgcoatingconservatively becausetheoriginalWulfS3explicitlysays1000kg/tonne; thereisnosourcedbasis to silentlyreplaceitbyZn ordeletea potentialbathchemical. Thisanomalouschemicalintensity remains a quantified sourcegap,not a closedindustrialrecipe. HeatCHPunit/source dust-factor anomalies arelikewiseunresolvedinexistingprocessreference; no fullprocesscertification. Thusnumericalmetalfeedisnowexplicitwhileuncertainnonmetalprocessburdensremainvisible. ExistingZn/othertraceemissionsretainedfromsource;subtractZnreleasefrommatchednetmetallosswasteforno doublemetal-lossaccount. Thisdoesnotbalanceunmeasuredtraceelementsinbathchemicals. No globalnativegalvanizingedit. Rewirebothpipelineconstructioncoatingpurchases tothis1kgfinishedcoatingprovider atunchanged446.05kg/km inthiscommit; issue73 separatelycorrects geometricdose andpolymer/lifecycleboundary. Originallegacycoatingprovider retainedforcompatibility andannotatedwithknownsourceproblem. ActualpipelineGalvalumegrade isdocumented55/43.4/1.6; layerthicknessandcoatedarea addressednext. Noassumedzerozincor unsupportedcredit.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 LCI of the process of applying 1 kg of zinc coating (Faist Emmenegger et al., 2007a, b; Krieg, 2012)</t>
         </is>
@@ -7111,7 +7113,7 @@
         <v>152</v>
       </c>
       <c r="B207" s="8">
-        <v>-1.4E-5</v>
+        <v>-0.0147</v>
       </c>
       <c r="C207" s="8" t="s">
         <v>41</v>
@@ -7125,12 +7127,17 @@
       <c r="G207" s="8" t="s">
         <v>154</v>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source specifies14.7kg dust landfill treatment per1000kg coating, so the correct purchase is-0.0147kg/kg,not-0.000014kg/kg (1050times smaller than the source). Keep the existing native EAF dust disposal market: its production is-1kg and the negative purchase activates positive treatment. No new recovery credit or supplier-route substitution is introduced. The source-treatment dust assay is unreported; its ownership versus the separate nominal95%alloy-yield reject budget remains unqualified. A corrected transcription does not establish element closure between mixed process residues and separately modelled alloy loss. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.</t>
+        </is>
+      </c>
       <c r="I207" s="8">
         <v>2</v>
       </c>
       <c r="J207">
         <f t="shared" ref="J207:J209" si="16">LN(B207*-1)</f>
-        <v>-11.176453228349015</v>
+        <v>-4.219907785197447</v>
       </c>
       <c r="K207" s="6">
         <v>1.5</v>
@@ -11977,7 +11984,9 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: Galvalume coating, retained alloy mass, engineering reference. Former reference product: Galvalume coating, retained alloy mass, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source specifies14.7kg dust landfill treatment per1000kg coating, so the correct purchase is-0.0147kg/kg,not-0.000014kg/kg (1050times smaller than the source). Keep the existing native EAF dust disposal market: its production is-1kg and the negative purchase activates positive treatment. No new recovery credit or supplier-route substitution is introduced. The source-treatment dust assay is unreported; its ownership versus the separate nominal95%alloy-yield reject budget remains unqualified. A corrected transcription does not establish element closure between mixed process residues and separately modelled alloy loss. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Nomenclature revision, 2026-10-19. Former activity name: Galvalume coating, retained alloy mass, engineering reference. Former reference product: Galvalume coating, retained alloy mass, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED EXPLICIT GALVALUME METAL FEED, issue72,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook. Introducea clearlydefined1kgretainedGalvalume coatingreference with0.55kgAl,0.434kgZn,0.016kgSi. Itisnot1kgpureZn,nor1kgcoatedsteel,andsodaashcannotprovideZn. UsegenericwroughtAl,marketZn andmetallurgicalSisupply; forming/galvanicalloying1kWh/kg explicitengineeringassemblyallowance.95%metalretention reference,test90-100%;grossfeeds=retained/.95,pairedmixedmanufacturingwaste=(1/.95-1)kgminusdeclaredZnrelease2.94e-5kg. DetailedZn/Al/Si-specificlossfatesunresolved; donot countallscrapasrecoverablemetal. Copyotherexistingpublicbathchemical/utility/emissionprocess coefficients as a DOCUMENTEDPROXY,not verifiedmodernapplicationdata. Inparticularretain1kgsodaash/kgcoatingconservatively becausetheoriginalWulfS3explicitlysays1000kg/tonne; thereisnosourcedbasis to silentlyreplaceitbyZn ordeletea potentialbathchemical. Thisanomalouschemicalintensity remains a quantified sourcegap,not a closedindustrialrecipe. HeatCHPunit/source dust-factor anomalies arelikewiseunresolvedinexistingprocessreference; no fullprocesscertification. Thusnumericalmetalfeedisnowexplicitwhileuncertainnonmetalprocessburdensremainvisible. ExistingZn/othertraceemissionsretainedfromsource;subtractZnreleasefrommatchednetmetallosswasteforno doublemetal-lossaccount. Thisdoesnotbalanceunmeasuredtraceelementsinbathchemicals. No globalnativegalvanizingedit. Rewirebothpipelineconstructioncoatingpurchases tothis1kgfinishedcoatingprovider atunchanged446.05kg/km inthiscommit; issue73 separatelycorrects geometricdose andpolymer/lifecycleboundary. Originallegacycoatingprovider retainedforcompatibility andannotatedwithknownsourceproblem. ActualpipelineGalvalumegrade isdocumented55/43.4/1.6; layerthicknessandcoatedarea addressednext. Noassumedzerozincor unsupportedcredit.</t>
         </is>
       </c>
@@ -12183,7 +12192,7 @@
         </is>
       </c>
       <c r="B401">
-        <v>-1.4e-05</v>
+        <v>-0.0147</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
@@ -12203,6 +12212,11 @@
       <c r="G401" t="inlineStr">
         <is>
           <t>electric arc furnace dust</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source specifies14.7kg dust landfill treatment per1000kg coating, so the correct purchase is-0.0147kg/kg,not-0.000014kg/kg (1050times smaller than the source). Keep the existing native EAF dust disposal market: its production is-1kg and the negative purchase activates positive treatment. No new recovery credit or supplier-route substitution is introduced. The source-treatment dust assay is unreported; its ownership versus the separate nominal95%alloy-yield reject budget remains unqualified. A corrected transcription does not establish element closure between mixed process residues and separately modelled alloy loss. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">

--- a/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
@@ -6983,7 +6983,9 @@
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source specifies14.7kg dust landfill treatment per1000kg coating, so the correct purchase is-0.0147kg/kg,not-0.000014kg/kg (1050times smaller than the source). Keep the existing native EAF dust disposal market: its production is-1kg and the negative purchase activates positive treatment. No new recovery credit or supplier-route substitution is introduced. The source-treatment dust assay is unreported; its ownership versus the separate nominal95%alloy-yield reject budget remains unqualified. A corrected transcription does not establish element closure between mixed process residues and separately modelled alloy loss. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.
+          <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source input is30.6g ammonia per1000kg coating,so buy 0.0000306kg/kg,not0.000036kg/kg. The former value corresponds to36g/t,a transcription error. Keep the existing nominal anhydrous-ammonia product basis; source solvent/purity and actual bath makeup remain unqualified. The separate source ammonia AIR EMISSION43.6g/t is unchanged:an input correction must not silently alter an independently reported emission. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source specifies14.7kg dust landfill treatment per1000kg coating, so the correct purchase is-0.0147kg/kg,not-0.000014kg/kg (1050times smaller than the source). Keep the existing native EAF dust disposal market: its production is-1kg and the negative purchase activates positive treatment. No new recovery credit or supplier-route substitution is introduced. The source-treatment dust assay is unreported; its ownership versus the separate nominal95%alloy-yield reject budget remains unqualified. A corrected transcription does not establish element closure between mixed process residues and separately modelled alloy loss. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED EXPLICIT GALVALUME METAL FEED, issue72,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook. Introducea clearlydefined1kgretainedGalvalume coatingreference with0.55kgAl,0.434kgZn,0.016kgSi. Itisnot1kgpureZn,nor1kgcoatedsteel,andsodaashcannotprovideZn. UsegenericwroughtAl,marketZn andmetallurgicalSisupply; forming/galvanicalloying1kWh/kg explicitengineeringassemblyallowance.95%metalretention reference,test90-100%;grossfeeds=retained/.95,pairedmixedmanufacturingwaste=(1/.95-1)kgminusdeclaredZnrelease2.94e-5kg. DetailedZn/Al/Si-specificlossfatesunresolved; donot countallscrapasrecoverablemetal. Copyotherexistingpublicbathchemical/utility/emissionprocess coefficients as a DOCUMENTEDPROXY,not verifiedmodernapplicationdata. Inparticularretain1kgsodaash/kgcoatingconservatively becausetheoriginalWulfS3explicitlysays1000kg/tonne; thereisnosourcedbasis to silentlyreplaceitbyZn ordeletea potentialbathchemical. Thisanomalouschemicalintensity remains a quantified sourcegap,not a closedindustrialrecipe. HeatCHPunit/source dust-factor anomalies arelikewiseunresolvedinexistingprocessreference; no fullprocesscertification. Thusnumericalmetalfeedisnowexplicitwhileuncertainnonmetalprocessburdensremainvisible. ExistingZn/othertraceemissionsretainedfromsource;subtractZnreleasefrommatchednetmetallosswasteforno doublemetal-lossaccount. Thisdoesnotbalanceunmeasuredtraceelementsinbathchemicals. No globalnativegalvanizingedit. Rewirebothpipelineconstructioncoatingpurchases tothis1kgfinishedcoatingprovider atunchanged446.05kg/km inthiscommit; issue73 separatelycorrects geometricdose andpolymer/lifecycleboundary. Originallegacycoatingprovider retainedforcompatibility andannotatedwithknownsourceproblem. ActualpipelineGalvalumegrade isdocumented55/43.4/1.6; layerthicknessandcoatedarea addressednext. Noassumedzerozincor unsupportedcredit.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -7449,7 +7451,7 @@
         <v>82</v>
       </c>
       <c r="B213" s="8">
-        <v>3.5999999999999994E-5</v>
+        <v>3.06e-05</v>
       </c>
       <c r="C213" s="8" t="s">
         <v>41</v>
@@ -7463,12 +7465,17 @@
       <c r="G213" s="8" t="s">
         <v>83</v>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source input is30.6g ammonia per1000kg coating,so buy 0.0000306kg/kg,not0.000036kg/kg. The former value corresponds to36g/t,a transcription error. Keep the existing nominal anhydrous-ammonia product basis; source solvent/purity and actual bath makeup remain unqualified. The separate source ammonia AIR EMISSION43.6g/t is unchanged:an input correction must not silently alter an independently reported emission. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.</t>
+        </is>
+      </c>
       <c r="I213" s="8">
         <v>2</v>
       </c>
       <c r="J213">
         <f t="shared" si="18"/>
-        <v>-10.231991619508165</v>
+        <v>-10.39451054900594</v>
       </c>
       <c r="K213" s="6">
         <v>1.5</v>
@@ -11984,7 +11991,9 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source specifies14.7kg dust landfill treatment per1000kg coating, so the correct purchase is-0.0147kg/kg,not-0.000014kg/kg (1050times smaller than the source). Keep the existing native EAF dust disposal market: its production is-1kg and the negative purchase activates positive treatment. No new recovery credit or supplier-route substitution is introduced. The source-treatment dust assay is unreported; its ownership versus the separate nominal95%alloy-yield reject budget remains unqualified. A corrected transcription does not establish element closure between mixed process residues and separately modelled alloy loss. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.
+          <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source input is30.6g ammonia per1000kg coating,so buy 0.0000306kg/kg,not0.000036kg/kg. The former value corresponds to36g/t,a transcription error. Keep the existing nominal anhydrous-ammonia product basis; source solvent/purity and actual bath makeup remain unqualified. The separate source ammonia AIR EMISSION43.6g/t is unchanged:an input correction must not silently alter an independently reported emission. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source specifies14.7kg dust landfill treatment per1000kg coating, so the correct purchase is-0.0147kg/kg,not-0.000014kg/kg (1050times smaller than the source). Keep the existing native EAF dust disposal market: its production is-1kg and the negative purchase activates positive treatment. No new recovery credit or supplier-route substitution is introduced. The source-treatment dust assay is unreported; its ownership versus the separate nominal95%alloy-yield reject budget remains unqualified. A corrected transcription does not establish element closure between mixed process residues and separately modelled alloy loss. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Nomenclature revision, 2026-10-19. Former activity name: Galvalume coating, retained alloy mass, engineering reference. Former reference product: Galvalume coating, retained alloy mass, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED EXPLICIT GALVALUME METAL FEED, issue72,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook. Introducea clearlydefined1kgretainedGalvalume coatingreference with0.55kgAl,0.434kgZn,0.016kgSi. Itisnot1kgpureZn,nor1kgcoatedsteel,andsodaashcannotprovideZn. UsegenericwroughtAl,marketZn andmetallurgicalSisupply; forming/galvanicalloying1kWh/kg explicitengineeringassemblyallowance.95%metalretention reference,test90-100%;grossfeeds=retained/.95,pairedmixedmanufacturingwaste=(1/.95-1)kgminusdeclaredZnrelease2.94e-5kg. DetailedZn/Al/Si-specificlossfatesunresolved; donot countallscrapasrecoverablemetal. Copyotherexistingpublicbathchemical/utility/emissionprocess coefficients as a DOCUMENTEDPROXY,not verifiedmodernapplicationdata. Inparticularretain1kgsodaash/kgcoatingconservatively becausetheoriginalWulfS3explicitlysays1000kg/tonne; thereisnosourcedbasis to silentlyreplaceitbyZn ordeletea potentialbathchemical. Thisanomalouschemicalintensity remains a quantified sourcegap,not a closedindustrialrecipe. HeatCHPunit/source dust-factor anomalies arelikewiseunresolvedinexistingprocessreference; no fullprocesscertification. Thusnumericalmetalfeedisnowexplicitwhileuncertainnonmetalprocessburdensremainvisible. ExistingZn/othertraceemissionsretainedfromsource;subtractZnreleasefrommatchednetmetallosswasteforno doublemetal-lossaccount. Thisdoesnotbalanceunmeasuredtraceelementsinbathchemicals. No globalnativegalvanizingedit. Rewirebothpipelineconstructioncoatingpurchases tothis1kgfinishedcoatingprovider atunchanged446.05kg/km inthiscommit; issue73 separatelycorrects geometricdose andpolymer/lifecycleboundary. Originallegacycoatingprovider retainedforcompatibility andannotatedwithknownsourceproblem. ActualpipelineGalvalumegrade isdocumented55/43.4/1.6; layerthicknessandcoatedarea addressednext. Noassumedzerozincor unsupportedcredit.</t>
@@ -12407,7 +12416,7 @@
         </is>
       </c>
       <c r="B407">
-        <v>3.5999999999999994e-05</v>
+        <v>3.06e-05</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
@@ -12427,6 +12436,11 @@
       <c r="G407" t="inlineStr">
         <is>
           <t>ammonia, anhydrous, liquid</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source input is30.6g ammonia per1000kg coating,so buy 0.0000306kg/kg,not0.000036kg/kg. The former value corresponds to36g/t,a transcription error. Keep the existing nominal anhydrous-ammonia product basis; source solvent/purity and actual bath makeup remain unqualified. The separate source ammonia AIR EMISSION43.6g/t is unchanged:an input correction must not silently alter an independently reported emission. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">

--- a/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-distribution.xlsx
@@ -1231,7 +1231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T454"/>
+  <dimension ref="A1:T457"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44.5" customWidth="1"/>
@@ -11512,69 +11512,36 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H375" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I375" t="inlineStr">
-        <is>
-          <t>product</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t xml:space="preserve">hydrogen storage tank system production, refuelling station, 125 kg hydrogen</t>
-        </is>
-      </c>
-      <c r="B376">
-        <v>1</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -11582,30 +11549,40 @@
           <t>unit</t>
         </is>
       </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t xml:space="preserve">hydrogen storage tank system, refuelling station, 125 kg hydrogen</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t xml:space="preserve">hydrogen storage tank system, refuelling station, 125 kg hydrogen</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>market for sheet rolling, aluminium</t>
+          <t xml:space="preserve">hydrogen storage tank system production, refuelling station, 125 kg hydrogen</t>
         </is>
       </c>
       <c r="B377">
-        <v>75.0</v>
+        <v>1</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -11614,29 +11591,29 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>sheet rolling, aluminium</t>
+          <t xml:space="preserve">hydrogen storage tank system, refuelling station, 125 kg hydrogen</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>sheet rolling, aluminium</t>
+          <t xml:space="preserve">hydrogen storage tank system, refuelling station, 125 kg hydrogen</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>market for aluminium, wrought alloy</t>
+          <t>market for sheet rolling, aluminium</t>
         </is>
       </c>
       <c r="B378">
@@ -11659,23 +11636,23 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t>sheet rolling, aluminium</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t>sheet rolling, aluminium</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>market for sheet rolling, chromium steel</t>
+          <t>market for aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="B379">
-        <v>112.5</v>
+        <v>75.0</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -11694,19 +11671,19 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>sheet rolling, chromium steel</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>sheet rolling, chromium steel</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>market for steel, chromium steel 18/8</t>
+          <t>market for sheet rolling, chromium steel</t>
         </is>
       </c>
       <c r="B380">
@@ -11729,27 +11706,27 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>steel, chromium steel 18/8</t>
+          <t>sheet rolling, chromium steel</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>steel, chromium steel 18/8</t>
+          <t>sheet rolling, chromium steel</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>carbon fiber production, weaved, at factory</t>
+          <t>market for steel, chromium steel 18/8</t>
         </is>
       </c>
       <c r="B381">
-        <v>892.5000000000001</v>
+        <v>112.5</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -11764,23 +11741,23 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>carbon fiber, weaved</t>
+          <t>steel, chromium steel 18/8</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>carbon fiber, weaved</t>
+          <t>steel, chromium steel 18/8</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>market for epoxy resin, liquid</t>
+          <t>carbon fiber production, weaved, at factory</t>
         </is>
       </c>
       <c r="B382">
-        <v>382.5</v>
+        <v>892.5000000000001</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -11799,23 +11776,23 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>epoxy resin, liquid</t>
+          <t>carbon fiber, weaved</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>epoxy resin, liquid</t>
+          <t>carbon fiber, weaved</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>market group for electricity, low voltage</t>
+          <t>market for epoxy resin, liquid</t>
         </is>
       </c>
       <c r="B383">
-        <v>56.25</v>
+        <v>382.5</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -11824,7 +11801,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -11834,32 +11811,32 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>electricity, low voltage</t>
+          <t>epoxy resin, liquid</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>electricity, low voltage</t>
+          <t>epoxy resin, liquid</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>market for sheet rolling, steel</t>
+          <t>market group for electricity, low voltage</t>
         </is>
       </c>
       <c r="B384">
-        <v>112.5</v>
+        <v>56.25</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>kilowatt hour</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -11869,19 +11846,19 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>sheet rolling, steel</t>
+          <t>electricity, low voltage</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>sheet rolling, steel</t>
+          <t>electricity, low voltage</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
+          <t>market for sheet rolling, steel</t>
         </is>
       </c>
       <c r="B385">
@@ -11904,92 +11881,127 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
+          <t>sheet rolling, steel</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>sheet rolling, steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B386">
+        <v>112.5</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
           <t>steel, low-alloyed</t>
         </is>
       </c>
-      <c r="I385" t="inlineStr">
+      <c r="I386" t="inlineStr">
         <is>
           <t>steel, low-alloyed</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aluminium-zinc coating alloy production, for galvanizing</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t xml:space="preserve">aluminium-zinc coating alloy production, for galvanizing</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B390">
-        <v>1</v>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aluminium-zinc coating alloy, for galvanizing</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B391">
+        <v>1</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t xml:space="preserve">aluminium-zinc coating alloy, for galvanizing</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook.</t>
+          <t>kilogram</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI https://ars.els-cdn.com/content/image/1-s2.0-S030626192201354X-mmc1.docx TableS4 explicitlyspecifiesGalvalume55wt%Al,43.4wt%Zn,1.6wt%Si. Wulf2018 publicSI TableS3 literal1tonnecoating tablelists1000kgsodaash andnoZnfeed;theanomaly originatesinpublishedSI,not onlythisworkbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
+      <c r="B395" t="inlineStr">
         <is>
           <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source input is30.6g ammonia per1000kg coating,so buy 0.0000306kg/kg,not0.000036kg/kg. The former value corresponds to36g/t,a transcription error. Keep the existing nominal anhydrous-ammonia product basis; source solvent/purity and actual bath makeup remain unqualified. The separate source ammonia AIR EMISSION43.6g/t is unchanged:an input correction must not silently alter an independently reported emission. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -12000,138 +12012,80 @@
         </is>
       </c>
     </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>name</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H396" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I396" t="inlineStr">
-        <is>
-          <t>product</t>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t xml:space="preserve">aluminium-zinc coating alloy production, for galvanizing</t>
-        </is>
-      </c>
-      <c r="B397">
-        <v>1</v>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aluminium-zinc coating alloy, for galvanizing</t>
-        </is>
-      </c>
-      <c r="I397" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aluminium-zinc coating alloy, for galvanizing</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>market for aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="B398">
-        <v>0.5789473684210527</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>market for zinc</t>
+          <t xml:space="preserve">aluminium-zinc coating alloy production, for galvanizing</t>
         </is>
       </c>
       <c r="B399">
-        <v>0.45684210526315794</v>
+        <v>1</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
@@ -12145,28 +12099,28 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>zinc</t>
+          <t xml:space="preserve">aluminium-zinc coating alloy, for galvanizing</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>zinc</t>
+          <t xml:space="preserve">aluminium-zinc coating alloy, for galvanizing</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>market for silicon, metallurgical grade</t>
+          <t>market for aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="B400">
-        <v>0.016842105263157894</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
@@ -12185,27 +12139,27 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>silicon, metallurgical grade</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>silicon, metallurgical grade</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>market for electric arc furnace dust</t>
+          <t>market for zinc</t>
         </is>
       </c>
       <c r="B401">
-        <v>-0.0147</v>
+        <v>0.45684210526315794</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -12220,32 +12174,27 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>electric arc furnace dust</t>
-        </is>
-      </c>
-      <c r="H401" t="inlineStr">
-        <is>
-          <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source specifies14.7kg dust landfill treatment per1000kg coating, so the correct purchase is-0.0147kg/kg,not-0.000014kg/kg (1050times smaller than the source). Keep the existing native EAF dust disposal market: its production is-1kg and the negative purchase activates positive treatment. No new recovery credit or supplier-route substitution is introduced. The source-treatment dust assay is unreported; its ownership versus the separate nominal95%alloy-yield reject budget remains unqualified. A corrected transcription does not establish element closure between mixed process residues and separately modelled alloy loss. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.</t>
+          <t>zinc</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>electric arc furnace dust</t>
+          <t>zinc</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>treatment of waste mineral oil, hazardous waste incineration</t>
+          <t>market for silicon, metallurgical grade</t>
         </is>
       </c>
       <c r="B402">
-        <v>-0.00016</v>
+        <v>0.016842105263157894</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Europe without Switzerland</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -12260,27 +12209,27 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>waste mineral oil</t>
+          <t>silicon, metallurgical grade</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>waste mineral oil</t>
+          <t>silicon, metallurgical grade</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>market for sludge from steel rolling</t>
+          <t>market for electric arc furnace dust</t>
         </is>
       </c>
       <c r="B403">
-        <v>-9.06e-05</v>
+        <v>-0.0147</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -12295,23 +12244,28 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>sludge from steel rolling</t>
+          <t>electric arc furnace dust</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source specifies14.7kg dust landfill treatment per1000kg coating, so the correct purchase is-0.0147kg/kg,not-0.000014kg/kg (1050times smaller than the source). Keep the existing native EAF dust disposal market: its production is-1kg and the negative purchase activates positive treatment. No new recovery credit or supplier-route substitution is introduced. The source-treatment dust assay is unreported; its ownership versus the separate nominal95%alloy-yield reject budget remains unqualified. A corrected transcription does not establish element closure between mixed process residues and separately modelled alloy loss. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>sludge from steel rolling</t>
+          <t>electric arc furnace dust</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>market for water, deionised</t>
+          <t>treatment of waste mineral oil, hazardous waste incineration</t>
         </is>
       </c>
       <c r="B404">
-        <v>0.2</v>
+        <v>-0.00016</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
@@ -12330,23 +12284,23 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>water, deionised</t>
+          <t>waste mineral oil</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>water, deionised</t>
+          <t>waste mineral oil</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>market for chemicals, inorganic</t>
+          <t>market for sludge from steel rolling</t>
         </is>
       </c>
       <c r="B405">
-        <v>0.0015</v>
+        <v>-9.06e-05</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
@@ -12365,27 +12319,27 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>chemical, inorganic</t>
+          <t>sludge from steel rolling</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>chemical, inorganic</t>
+          <t>sludge from steel rolling</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>market for aluminium sulfate, powder</t>
+          <t>market for water, deionised</t>
         </is>
       </c>
       <c r="B406">
-        <v>9.06e-07</v>
+        <v>0.2</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>Europe without Switzerland</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -12400,27 +12354,27 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>aluminium sulfate, powder</t>
+          <t>water, deionised</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>aluminium sulfate, powder</t>
+          <t>water, deionised</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>market for ammonia, anhydrous, liquid</t>
+          <t>market for chemicals, inorganic</t>
         </is>
       </c>
       <c r="B407">
-        <v>3.06e-05</v>
+        <v>0.0015</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -12435,37 +12389,32 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>ammonia, anhydrous, liquid</t>
-        </is>
-      </c>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source input is30.6g ammonia per1000kg coating,so buy 0.0000306kg/kg,not0.000036kg/kg. The former value corresponds to36g/t,a transcription error. Keep the existing nominal anhydrous-ammonia product basis; source solvent/purity and actual bath makeup remain unqualified. The separate source ammonia AIR EMISSION43.6g/t is unchanged:an input correction must not silently alter an independently reported emission. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.</t>
+          <t>chemical, inorganic</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>ammonia, anhydrous, liquid</t>
+          <t>chemical, inorganic</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>heat production, light fuel oil, at boiler 100kW, non-modulating</t>
+          <t>market for aluminium sulfate, powder</t>
         </is>
       </c>
       <c r="B408">
-        <v>0.768</v>
+        <v>9.06e-07</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Europe without Switzerland</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>megajoule</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -12475,23 +12424,23 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>heat, central or small-scale, other than natural gas</t>
+          <t>aluminium sulfate, powder</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>heat, central or small-scale, other than natural gas</t>
+          <t>aluminium sulfate, powder</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>market for heat, from steam, in chemical industry</t>
+          <t>market for ammonia, anhydrous, liquid</t>
         </is>
       </c>
       <c r="B409">
-        <v>0.0201</v>
+        <v>3.06e-05</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
@@ -12500,7 +12449,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>megajoule</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -12510,32 +12459,37 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>heat, from steam, in chemical industry</t>
+          <t>ammonia, anhydrous, liquid</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>WULF2018 TABLE S3 INPUT TRANSCRIPTION CORRECTION,2026-10-20. The source input is30.6g ammonia per1000kg coating,so buy 0.0000306kg/kg,not0.000036kg/kg. The former value corresponds to36g/t,a transcription error. Keep the existing nominal anhydrous-ammonia product basis; source solvent/purity and actual bath makeup remain unqualified. The separate source ammonia AIR EMISSION43.6g/t is unchanged:an input correction must not silently alter an independently reported emission. Source:Life Cycle Assessment of hydrogen transport and distribution options,DOI10.1016/j.jclepro.2018.07.180,TableS3(LCI of1t zinc coating forGalvalume),https://ars.els-cdn.com/content/image/1-s2.0-S095965261832170X-mmc1.docx. Retain every other input,emission, coating composition,dose,pipeline geometry,service and EOL quantity. Where a lognormal loc formula exists,retain its exact formula and update its cached ln(abs(amount));relative spread and negative flag remain unchanged. This applies to the existing compatibility reference and its copied process input in the explicit Galvalume provider. It does not validate the compatibility recipe as complete zinc supply or industrial coating data. Published soda-ash,CHP-unit, powder/FBE processing and waste-assay gaps remain open. Existing supplemental workbook only;no runtime,YAML or method edits.</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>heat, from steam, in chemical industry</t>
+          <t>ammonia, anhydrous, liquid</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>market for hydrochloric acid, without water, in 30% solution state</t>
+          <t>heat production, light fuel oil, at boiler 100kW, non-modulating</t>
         </is>
       </c>
       <c r="B410">
-        <v>0.0222</v>
+        <v>0.768</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>Europe without Switzerland</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>megajoule</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -12545,27 +12499,27 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>hydrochloric acid, without water, in 30% solution state</t>
+          <t>heat, central or small-scale, other than natural gas</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>hydrochloric acid, without water, in 30% solution state</t>
+          <t>heat, central or small-scale, other than natural gas</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>market for heat, central or small-scale, natural gas</t>
+          <t>market for heat, from steam, in chemical industry</t>
         </is>
       </c>
       <c r="B411">
-        <v>0.768</v>
+        <v>0.0201</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Europe without Switzerland</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -12580,32 +12534,32 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>heat, central or small-scale, natural gas</t>
+          <t>heat, from steam, in chemical industry</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>heat, central or small-scale, natural gas</t>
+          <t>heat, from steam, in chemical industry</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>market for rolling mill</t>
+          <t>market for hydrochloric acid, without water, in 30% solution state</t>
         </is>
       </c>
       <c r="B412">
-        <v>1.63e-13</v>
+        <v>0.0222</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -12615,32 +12569,32 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>rolling mill</t>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>rolling mill</t>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>market for soda ash, light, crystalline, heptahydrate</t>
+          <t>market for heat, central or small-scale, natural gas</t>
         </is>
       </c>
       <c r="B413">
-        <v>1</v>
+        <v>0.768</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>Europe without Switzerland</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>megajoule</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -12650,23 +12604,23 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>soda ash, light, crystalline, heptahydrate</t>
+          <t>heat, central or small-scale, natural gas</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>soda ash, light, crystalline, heptahydrate</t>
+          <t>heat, central or small-scale, natural gas</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>market for sodium hydroxide, without water, in 50% solution state</t>
+          <t>market for rolling mill</t>
         </is>
       </c>
       <c r="B414">
-        <v>0.00038</v>
+        <v>1.63e-13</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
@@ -12675,7 +12629,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -12685,32 +12639,32 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>sodium hydroxide, without water, in 50% solution state</t>
+          <t>rolling mill</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>sodium hydroxide, without water, in 50% solution state</t>
+          <t>rolling mill</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>market for transport, freight, lorry, unspecified</t>
+          <t>market for soda ash, light, crystalline, heptahydrate</t>
         </is>
       </c>
       <c r="B415">
-        <v>0.008039999999999999</v>
+        <v>1</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>ton kilometer</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -12720,32 +12674,32 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>transport, freight, lorry, unspecified</t>
+          <t>soda ash, light, crystalline, heptahydrate</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>transport, freight, lorry, unspecified</t>
+          <t>soda ash, light, crystalline, heptahydrate</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>market group for electricity, low voltage</t>
+          <t>market for sodium hydroxide, without water, in 50% solution state</t>
         </is>
       </c>
       <c r="B416">
-        <v>0.02033333333333333</v>
+        <v>0.00038</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -12755,32 +12709,32 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>electricity, low voltage</t>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>electricity, low voltage</t>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>market for hazardous waste, for incineration</t>
+          <t>market for transport, freight, lorry, unspecified</t>
         </is>
       </c>
       <c r="B417">
-        <v>-0.052602178947368364</v>
+        <v>0.008039999999999999</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>ton kilometer</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -12790,27 +12744,27 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>hazardous waste, for incineration</t>
+          <t>transport, freight, lorry, unspecified</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>hazardous waste, for incineration</t>
+          <t>transport, freight, lorry, unspecified</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t>market group for electricity, low voltage</t>
         </is>
       </c>
       <c r="B418">
-        <v>1</v>
+        <v>0.02033333333333333</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -12825,83 +12779,93 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>electricity, low voltage</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>electricity, low voltage</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>market for hazardous waste, for incineration</t>
         </is>
       </c>
       <c r="B419">
-        <v>4.36e-05</v>
+        <v>-0.052602178947368364</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>air</t>
-        </is>
-      </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>biosphere</t>
-        </is>
-      </c>
-      <c r="H419" t="inlineStr">
-        <is>
-          <t/>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Arsenic ion</t>
+          <t>market group for electricity, medium voltage</t>
         </is>
       </c>
       <c r="B420">
-        <v>1.9000000000000002e-10</v>
+        <v>1</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>air</t>
+          <t>kilowatt hour</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>biosphere</t>
-        </is>
-      </c>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t/>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>BOD5, Biological Oxygen Demand</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B421">
-        <v>1.32e-05</v>
+        <v>4.36e-05</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -12910,7 +12874,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>water::ground-</t>
+          <t>air</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -12927,11 +12891,11 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Cadmium II</t>
+          <t>Arsenic ion</t>
         </is>
       </c>
       <c r="B422">
-        <v>1.31e-09</v>
+        <v>1.9000000000000002e-10</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -12957,11 +12921,11 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>COD, Chemical Oxygen Demand</t>
+          <t>BOD5, Biological Oxygen Demand</t>
         </is>
       </c>
       <c r="B423">
-        <v>0.000132</v>
+        <v>1.32e-05</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -12987,11 +12951,11 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Chloride</t>
+          <t>Cadmium II</t>
         </is>
       </c>
       <c r="B424">
-        <v>1.88e-06</v>
+        <v>1.31e-09</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -13000,7 +12964,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>water::ground-</t>
+          <t>air</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -13017,11 +12981,11 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Chromium VI</t>
+          <t>COD, Chemical Oxygen Demand</t>
         </is>
       </c>
       <c r="B425">
-        <v>7.6e-09</v>
+        <v>0.000132</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -13047,11 +13011,11 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Particulate Matter, &gt; 10 um</t>
+          <t>Chloride</t>
         </is>
       </c>
       <c r="B426">
-        <v>0.000157</v>
+        <v>1.88e-06</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -13060,7 +13024,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>water::ground-</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -13077,11 +13041,11 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Particulate Matter, &gt; 2.5 um and &lt; 10um</t>
+          <t>Chromium VI</t>
         </is>
       </c>
       <c r="B427">
-        <v>0.00762</v>
+        <v>7.6e-09</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -13090,7 +13054,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>water::ground-</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -13107,11 +13071,11 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Hydrocarbons, unspecified</t>
+          <t>Particulate Matter, &gt; 10 um</t>
         </is>
       </c>
       <c r="B428">
-        <v>1.1900000000000001e-07</v>
+        <v>0.000157</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -13120,7 +13084,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>water::ground-</t>
+          <t>air</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -13137,11 +13101,11 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Hydrochloric acid</t>
+          <t>Particulate Matter, &gt; 2.5 um and &lt; 10um</t>
         </is>
       </c>
       <c r="B429">
-        <v>1.83e-05</v>
+        <v>0.00762</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -13167,11 +13131,11 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Iron ion</t>
+          <t>Hydrocarbons, unspecified</t>
         </is>
       </c>
       <c r="B430">
-        <v>1.4e-06</v>
+        <v>1.1900000000000001e-07</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -13180,7 +13144,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>water::ground-</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -13197,11 +13161,11 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Iron ion</t>
+          <t>Hydrochloric acid</t>
         </is>
       </c>
       <c r="B431">
-        <v>5.649999999999999e-06</v>
+        <v>1.83e-05</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -13210,7 +13174,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>water::ground-</t>
+          <t>air</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -13227,11 +13191,11 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Lead II</t>
+          <t>Iron ion</t>
         </is>
       </c>
       <c r="B432">
-        <v>3.4000000000000003e-09</v>
+        <v>1.4e-06</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -13257,11 +13221,11 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Lead II</t>
+          <t>Iron ion</t>
         </is>
       </c>
       <c r="B433">
-        <v>1.51e-09</v>
+        <v>5.649999999999999e-06</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -13287,11 +13251,11 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Nickel II</t>
+          <t>Lead II</t>
         </is>
       </c>
       <c r="B434">
-        <v>9.999999999999999e-10</v>
+        <v>3.4000000000000003e-09</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -13300,7 +13264,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>water::ground-</t>
+          <t>air</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -13317,11 +13281,11 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Oils, unspecified</t>
+          <t>Lead II</t>
         </is>
       </c>
       <c r="B435">
-        <v>1.0399999999999999e-07</v>
+        <v>1.51e-09</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -13347,11 +13311,11 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Phosphorus</t>
+          <t>Nickel II</t>
         </is>
       </c>
       <c r="B436">
-        <v>9.000000000000001e-08</v>
+        <v>9.999999999999999e-10</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -13377,11 +13341,11 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Suspended solids, unspecified</t>
+          <t>Oils, unspecified</t>
         </is>
       </c>
       <c r="B437">
-        <v>2.24e-07</v>
+        <v>1.0399999999999999e-07</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -13407,11 +13371,11 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>TOC, Total Organic Carbon</t>
+          <t>Phosphorus</t>
         </is>
       </c>
       <c r="B438">
-        <v>2.97e-07</v>
+        <v>9.000000000000001e-08</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -13437,11 +13401,11 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Zinc II</t>
+          <t>Suspended solids, unspecified</t>
         </is>
       </c>
       <c r="B439">
-        <v>2.75e-05</v>
+        <v>2.24e-07</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -13450,7 +13414,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>water::ground-</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -13467,270 +13431,342 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
+          <t>TOC, Total Organic Carbon</t>
+        </is>
+      </c>
+      <c r="B440">
+        <v>2.97e-07</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>water::ground-</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
           <t>Zinc II</t>
         </is>
       </c>
-      <c r="B440">
+      <c r="B441">
+        <v>2.75e-05</v>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Zinc II</t>
+        </is>
+      </c>
+      <c r="B442">
         <v>1.9e-06</v>
       </c>
-      <c r="D440" t="inlineStr">
+      <c r="D442" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="E440" t="inlineStr">
+      <c r="E442" t="inlineStr">
         <is>
           <t>water::ground-</t>
         </is>
       </c>
-      <c r="F440" t="inlineStr">
+      <c r="F442" t="inlineStr">
         <is>
           <t>biosphere</t>
         </is>
       </c>
-      <c r="H440" t="inlineStr">
+      <c r="H442" t="inlineStr">
         <is>
           <t/>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t xml:space="preserve">polyethylene coating production, high density, for pipelines</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B445">
-        <v>1</v>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">polyethylene coating production, high density, for pipelines</t>
+        </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t xml:space="preserve">polyethylene coating, high density, for pipelines</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B447">
+        <v>1</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly.</t>
+          <t xml:space="preserve">polyethylene coating, high density, for pipelines</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B449" t="inlineStr">
+      <c r="B451" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: HDPE pipeline coat, material and extrusion, engineering reference. Former reference product: HDPE pipeline coat, material and extrusion, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED HYDROGEN PIPELINE GEOMETRY AND MATERIAL BOUNDARY, issue73,2026-10-18. Tsiklios2022 DOI10.1016/j.apenergy.2022.120097 publicSI TableS4:Galvalume55Al/43.4Zn/1.6Siwt%,150umFBE,HDPEfeedplus extrusion. Retain published transmission steel791447.36kg/km,innerGalvalumearea3660m2/km,HDPE5599.17kg/km. Existing PSI2023 distribution adaptation OD0.105m/ID0.100m fixes steelwall2.5mm; absolute coating thicknesses65um inner,25um outerpowder,0.5mmHDPE selected explicitly. Distribution selection is an explicit engineering adaptation,not an independently pressure-certified19bar pipeline:OD105mm,ID100mm=&gt;wall2.5mm,not copied4.5mm or27.09*(5/55). Steel density7850kg/m3 gives6319.509972236697kg/km; buy steel material AND equal pipe-drawing service,not two steel material inputs. Galvalume retainedmass=innerarea*pi*ID*length*65um*alloydensity; idealvolume-additive density=1/(.55/2700+.434/7140+.016/2330)=3685.2098164751933kg/m3. Transmission innerarea3660m2 fromsource gives876.7114153394484kg/km; distribution innerarea314.159m2 gives75.25328256144047kg/km. Thickness65um and idealalloydensity are explicitreferencechoices; actualmeasuredcoatingdensity/roughness/porosity need verification,test thickness30-100um. SourceGalvalume is reportedm2,notkg:original446.05kg cannot be transferred unchangedacrossdiameters. Both now buy issue72kgretainedalloy provider; its95%metalyield and unresolvedsodaash/processanomalies remainvisible. HDPEannulus outside25umFBE and0.5mmHDPE at950kg/m3 gives157.50767467854035kg/km; feedfullHDPEgranulateandmatchingextrusionservice,notextrusiononly. Transmission5599.17kgHDPE retainedassourced,not rederived underdistributiongeometry. NewHDPEprovider100%retentionreference,processscrap/yieldgapexplicit,test95-100%; no inventednegativeplasticcredit. Powdercoating native reference documents80um architecturalpowder,NOT source-specificFBE:purchase actualouterarea*selectedthickness/80um (25distribution,150transmission). This is an explicit thickness-proportional equivalent-area proxy including utilities; actualFBEresin/hardener,curingenergyperarea andservice-life gaps remain,not claimed industrialFBEreconstruction. Neither the addedHDPEfeed nor the coatservice includessteelmaterial. Freightretainseachoriginalimpliedmass-distance route for steel+Galvalume+HDPE,updatingtkmfornewretainedmass; excludesunknownpowder-retainedmass/sandfreight,asbefore. Distributiontrenchvolumes,sand,landuse/water andhelicoptersremainexistingperkmreferences ratherthan blindlyscaledbydiameteror100; trenchwidth andactualinstallationneedfieldvalidation. Service40years/0.22MtH2 and19bar distributionassumption retained,hydraulicsnotrecalculated; transmission40years/124.81Mtandcompressor125kmspacing unchanged. Treatment alreadyhas -1kmproduction andwrapper-1kmwasteinput:correctsigns preserved,not invertedorduplicated. Retainexisting50%landfill/treatment scenario as engineeringboundary,nowhalfretainedsteel+Galvalumemass toexistingdecommissionedpipeline treatment andhalfHDPE toexistingplastic treatment. Otherhalfmetal/polymerfate andpowdercoatingtreatment remainunresolved; no assumedprimary-secondaryshare,recoverycreditorclaimofcompleteEOLcoverage. Genericpipelinewastetreatment maycontainits ownlegacycomposition; not element-specificGalvalume recovery. Correctonlymisleadingdistributionmetadata; nativeprocesses/runtime/YAML unchanged. Geometry-derivedquantities:{'steel_kg_per_km': 6319.509972236697, 'Galvalume_kg_per_km': 75.25328256144047, 'HDPE_kg_per_km': 157.50767467854035}.</t>
         </is>
       </c>
     </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E451" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G451" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I451" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t xml:space="preserve">polyethylene coating production, high density, for pipelines</t>
-        </is>
-      </c>
-      <c r="B452">
-        <v>1</v>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F452" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G452" t="inlineStr">
-        <is>
-          <t xml:space="preserve">polyethylene coating, high density, for pipelines</t>
-        </is>
-      </c>
-      <c r="I452" t="inlineStr">
-        <is>
-          <t xml:space="preserve">polyethylene coating, high density, for pipelines</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>market for polyethylene, high density, granulate</t>
-        </is>
-      </c>
-      <c r="B453">
-        <v>1</v>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G453" t="inlineStr">
-        <is>
-          <t>polyethylene, high density, granulate</t>
-        </is>
-      </c>
-      <c r="I453" t="inlineStr">
-        <is>
-          <t>polyethylene, high density, granulate</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">polyethylene coating production, high density, for pipelines</t>
+        </is>
+      </c>
+      <c r="B455">
+        <v>1</v>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">polyethylene coating, high density, for pipelines</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">polyethylene coating, high density, for pipelines</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B456">
+        <v>1</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
           <t>extrusion, plastic film</t>
         </is>
       </c>
-      <c r="B454">
+      <c r="B457">
         <v>1</v>
       </c>
-      <c r="C454" t="inlineStr">
+      <c r="C457" t="inlineStr">
         <is>
           <t>RER</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr">
+      <c r="D457" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F454" t="inlineStr">
+      <c r="F457" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G454" t="inlineStr">
+      <c r="G457" t="inlineStr">
         <is>
           <t>extrusion, plastic film</t>
         </is>
       </c>
-      <c r="I454" t="inlineStr">
+      <c r="I457" t="inlineStr">
         <is>
           <t>extrusion, plastic film</t>
         </is>
